--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,27 +445,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>492546000</v>
+        <v>584494000</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>357420001</v>
+        <v>449821000</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>353366000</v>
+        <v>397825001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>213282000</v>
+        <v>285462000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,34 +526,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>73800000</v>
+        <v>90150000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>58350000</v>
+        <v>41100000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -562,28 +562,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>40100000</v>
+        <v>31700000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>8600000</v>
+        <v>6000000</v>
       </c>
     </row>
   </sheetData>
@@ -635,55 +635,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>489450000</v>
+        <v>189750000</v>
       </c>
       <c r="D2" t="n">
-        <v>2371</v>
+        <v>2044</v>
       </c>
       <c r="E2" t="n">
-        <v>3396586000</v>
+        <v>2487797000</v>
       </c>
       <c r="F2" t="n">
-        <v>366536000</v>
+        <v>245552000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>402450000</v>
+        <v>151400000</v>
       </c>
       <c r="D3" t="n">
-        <v>2547</v>
+        <v>2334</v>
       </c>
       <c r="E3" t="n">
-        <v>3184000000</v>
+        <v>3268954000</v>
       </c>
       <c r="F3" t="n">
-        <v>500801000</v>
+        <v>386936000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,40 +692,40 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>378400000</v>
+        <v>98700000</v>
       </c>
       <c r="D4" t="n">
-        <v>2179</v>
+        <v>2170</v>
       </c>
       <c r="E4" t="n">
-        <v>2810718000</v>
+        <v>2634535000</v>
       </c>
       <c r="F4" t="n">
-        <v>365495000</v>
+        <v>360885000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>353250000</v>
+        <v>86100000</v>
       </c>
       <c r="D5" t="n">
-        <v>2013</v>
+        <v>2495</v>
       </c>
       <c r="E5" t="n">
-        <v>2545372000</v>
+        <v>3002652000</v>
       </c>
       <c r="F5" t="n">
-        <v>217672000</v>
+        <v>503001000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>98000000</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="H2" t="n">
-        <v>607775000</v>
+        <v>546945000</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>39100000</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +873,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>73800000</v>
+        <v>3000000</v>
       </c>
       <c r="G3" t="n">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="H3" t="n">
-        <v>538240000</v>
+        <v>519207000</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="J3" t="n">
-        <v>4320000</v>
+        <v>69100000</v>
       </c>
       <c r="K3" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="L3" t="n">
-        <v>179296000</v>
+        <v>182716000</v>
       </c>
       <c r="M3" t="n">
-        <v>33.31</v>
+        <v>35.19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,31 +929,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="H4" t="n">
-        <v>196080000</v>
+        <v>177870000</v>
       </c>
       <c r="I4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J4" t="n">
-        <v>5040000</v>
+        <v>12270000</v>
       </c>
       <c r="K4" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L4" t="n">
-        <v>134105000</v>
+        <v>131300000</v>
       </c>
       <c r="M4" t="n">
-        <v>68.39</v>
+        <v>73.81999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,25 +967,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>109250000</v>
+        <v>48600000</v>
       </c>
       <c r="G5" t="n">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H5" t="n">
-        <v>822860000</v>
+        <v>790710000</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="J5" t="n">
-        <v>2100000</v>
+        <v>187600000</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
@@ -994,13 +994,13 @@
         <v>27995000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F6" t="n">
-        <v>64900000</v>
+        <v>30900000</v>
       </c>
       <c r="G6" t="n">
         <v>527</v>
       </c>
       <c r="H6" t="n">
-        <v>464600000</v>
+        <v>464770000</v>
       </c>
       <c r="I6" t="n">
-        <v>26</v>
+        <v>152</v>
       </c>
       <c r="J6" t="n">
-        <v>20190000</v>
+        <v>119900000</v>
       </c>
       <c r="K6" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L6" t="n">
-        <v>112580000</v>
+        <v>114165000</v>
       </c>
       <c r="M6" t="n">
-        <v>24.23</v>
+        <v>24.56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,25 +1061,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>56500000</v>
+        <v>3600000</v>
       </c>
       <c r="G7" t="n">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="H7" t="n">
-        <v>554445000</v>
+        <v>503150000</v>
       </c>
       <c r="I7" t="n">
-        <v>90</v>
+        <v>248</v>
       </c>
       <c r="J7" t="n">
-        <v>87380000</v>
+        <v>195855000</v>
       </c>
       <c r="K7" t="n">
         <v>39</v>
@@ -1088,13 +1088,13 @@
         <v>46825000</v>
       </c>
       <c r="M7" t="n">
-        <v>8.449999999999999</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,40 +1108,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>50700000</v>
+        <v>5400000</v>
       </c>
       <c r="G8" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="H8" t="n">
-        <v>380822000</v>
+        <v>360184000</v>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="J8" t="n">
-        <v>20250000</v>
+        <v>62455000</v>
       </c>
       <c r="K8" t="n">
         <v>161</v>
       </c>
       <c r="L8" t="n">
-        <v>123090000</v>
+        <v>121510000</v>
       </c>
       <c r="M8" t="n">
-        <v>32.32</v>
+        <v>33.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1155,40 +1155,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>56400000</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>132</v>
       </c>
       <c r="H9" t="n">
-        <v>159450000</v>
+        <v>153285000</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>3600000</v>
       </c>
       <c r="K9" t="n">
         <v>53</v>
       </c>
       <c r="L9" t="n">
-        <v>42760000</v>
+        <v>42210000</v>
       </c>
       <c r="M9" t="n">
-        <v>26.82</v>
+        <v>27.54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>46000000</v>
+        <v>10800000</v>
       </c>
       <c r="G10" t="n">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="H10" t="n">
-        <v>594380000</v>
+        <v>527898000</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="J10" t="n">
-        <v>12800000</v>
+        <v>58550000</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>1750000</v>
+        <v>1550000</v>
       </c>
       <c r="M10" t="n">
         <v>0.29</v>
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,40 +1249,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F11" t="n">
-        <v>119100000</v>
+        <v>61800000</v>
       </c>
       <c r="G11" t="n">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H11" t="n">
-        <v>877002000</v>
+        <v>839158000</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>62710000</v>
       </c>
       <c r="K11" t="n">
         <v>17</v>
       </c>
       <c r="L11" t="n">
-        <v>26775000</v>
+        <v>26225000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,40 +1296,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="F12" t="n">
-        <v>62700000</v>
+        <v>20700000</v>
       </c>
       <c r="G12" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="H12" t="n">
-        <v>424469000</v>
+        <v>401715000</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>26890000</v>
       </c>
       <c r="K12" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L12" t="n">
-        <v>58115000</v>
+        <v>57305000</v>
       </c>
       <c r="M12" t="n">
-        <v>13.69</v>
+        <v>14.27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,40 +1343,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>43500000</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="H13" t="n">
-        <v>374595000</v>
+        <v>352295000</v>
       </c>
       <c r="I13" t="n">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="J13" t="n">
-        <v>22310000</v>
+        <v>75810000</v>
       </c>
       <c r="K13" t="n">
         <v>138</v>
       </c>
       <c r="L13" t="n">
-        <v>113005000</v>
+        <v>112085000</v>
       </c>
       <c r="M13" t="n">
-        <v>30.17</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,40 +1390,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F14" t="n">
-        <v>97050000</v>
+        <v>56400000</v>
       </c>
       <c r="G14" t="n">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H14" t="n">
-        <v>736609000</v>
+        <v>729714000</v>
       </c>
       <c r="I14" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="J14" t="n">
-        <v>14875000</v>
+        <v>121565000</v>
       </c>
       <c r="K14" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="L14" t="n">
-        <v>64661000</v>
+        <v>72786000</v>
       </c>
       <c r="M14" t="n">
-        <v>8.779999999999999</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1437,40 +1437,40 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>90600000</v>
+        <v>24000000</v>
       </c>
       <c r="G15" t="n">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="H15" t="n">
-        <v>555870000</v>
+        <v>539380000</v>
       </c>
       <c r="I15" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="J15" t="n">
-        <v>17500000</v>
+        <v>62900000</v>
       </c>
       <c r="K15" t="n">
         <v>50</v>
       </c>
       <c r="L15" t="n">
-        <v>73775000</v>
+        <v>87725000</v>
       </c>
       <c r="M15" t="n">
-        <v>13.27</v>
+        <v>16.26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1484,40 +1484,40 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>71800000</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H16" t="n">
-        <v>415165000</v>
+        <v>386765000</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="J16" t="n">
-        <v>4335000</v>
+        <v>31820000</v>
       </c>
       <c r="K16" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L16" t="n">
-        <v>123600000</v>
+        <v>125825000</v>
       </c>
       <c r="M16" t="n">
-        <v>29.77</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,40 +1531,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="F17" t="n">
-        <v>118800000</v>
+        <v>23700000</v>
       </c>
       <c r="G17" t="n">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="H17" t="n">
-        <v>1006878000</v>
+        <v>957664000</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>194</v>
       </c>
       <c r="J17" t="n">
-        <v>43450000</v>
+        <v>303394000</v>
       </c>
       <c r="K17" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="L17" t="n">
-        <v>46550000</v>
+        <v>42650000</v>
       </c>
       <c r="M17" t="n">
-        <v>4.62</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,25 +1578,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="F18" t="n">
-        <v>111200000</v>
+        <v>47300000</v>
       </c>
       <c r="G18" t="n">
-        <v>591</v>
+        <v>576</v>
       </c>
       <c r="H18" t="n">
-        <v>682064000</v>
+        <v>655431000</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>75192000</v>
       </c>
       <c r="K18" t="n">
         <v>61</v>
@@ -1605,13 +1605,13 @@
         <v>57950000</v>
       </c>
       <c r="M18" t="n">
-        <v>8.5</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1625,25 +1625,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F19" t="n">
-        <v>62250000</v>
+        <v>66750000</v>
       </c>
       <c r="G19" t="n">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="H19" t="n">
-        <v>484825000</v>
+        <v>488105000</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>51775000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1672,25 +1672,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>59400000</v>
+        <v>4500000</v>
       </c>
       <c r="G20" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H20" t="n">
-        <v>390740000</v>
+        <v>360775000</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="J20" t="n">
-        <v>7500000</v>
+        <v>52125000</v>
       </c>
       <c r="K20" t="n">
         <v>62</v>
@@ -1699,13 +1699,13 @@
         <v>63370000</v>
       </c>
       <c r="M20" t="n">
-        <v>16.22</v>
+        <v>17.56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,40 +1719,40 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>47700000</v>
+        <v>8100000</v>
       </c>
       <c r="G21" t="n">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="H21" t="n">
-        <v>496897000</v>
+        <v>466837000</v>
       </c>
       <c r="I21" t="n">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="J21" t="n">
-        <v>30520000</v>
+        <v>143345000</v>
       </c>
       <c r="K21" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="L21" t="n">
-        <v>71542000</v>
+        <v>87972000</v>
       </c>
       <c r="M21" t="n">
-        <v>14.4</v>
+        <v>18.84</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,40 +1766,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F22" t="n">
-        <v>102900000</v>
+        <v>72900000</v>
       </c>
       <c r="G22" t="n">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="H22" t="n">
-        <v>780975000</v>
+        <v>774520000</v>
       </c>
       <c r="I22" t="n">
-        <v>17</v>
+        <v>128</v>
       </c>
       <c r="J22" t="n">
-        <v>33950000</v>
+        <v>147110000</v>
       </c>
       <c r="K22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L22" t="n">
-        <v>45475000</v>
+        <v>56975000</v>
       </c>
       <c r="M22" t="n">
-        <v>5.82</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1813,40 +1813,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F23" t="n">
-        <v>10500000</v>
+        <v>25500000</v>
       </c>
       <c r="G23" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H23" t="n">
-        <v>48560000</v>
+        <v>70060000</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>1500000</v>
+        <v>250000</v>
       </c>
       <c r="K23" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="L23" t="n">
-        <v>28910000</v>
+        <v>28860000</v>
       </c>
       <c r="M23" t="n">
-        <v>59.53</v>
+        <v>41.19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,25 +1860,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>70500000</v>
+        <v>12000000</v>
       </c>
       <c r="G24" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H24" t="n">
-        <v>343375000</v>
+        <v>327500000</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>45975000</v>
       </c>
       <c r="K24" t="n">
         <v>14</v>
@@ -1887,7 +1887,7 @@
         <v>8375000</v>
       </c>
       <c r="M24" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
     </row>
   </sheetData>
@@ -2192,10 +2192,10 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>489450000</v>
+        <v>151400000</v>
       </c>
       <c r="Q2" t="n">
-        <v>353366000</v>
+        <v>449821000</v>
       </c>
     </row>
     <row r="3">
@@ -2243,10 +2243,10 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>353250000</v>
+        <v>189750000</v>
       </c>
       <c r="Q3" t="n">
-        <v>213282000</v>
+        <v>285462000</v>
       </c>
     </row>
     <row r="4">
@@ -2294,10 +2294,10 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>402450000</v>
+        <v>86100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>492546000</v>
+        <v>584494000</v>
       </c>
     </row>
     <row r="5">
@@ -2345,10 +2345,10 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>378400000</v>
+        <v>98700000</v>
       </c>
       <c r="Q5" t="n">
-        <v>357420001</v>
+        <v>397825001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>584494000</v>
+        <v>568804000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>449821000</v>
+        <v>420968000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>397825001</v>
+        <v>377995001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>285462000</v>
+        <v>263437000</v>
       </c>
     </row>
   </sheetData>
@@ -517,61 +517,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>90150000</v>
+        <v>243100000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="D3" t="n">
-        <v>41100000</v>
+        <v>199590000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>31700000</v>
+        <v>141200000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>6000000</v>
+        <v>107500000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>189750000</v>
+        <v>196650000</v>
       </c>
       <c r="D2" t="n">
-        <v>2044</v>
+        <v>2040</v>
       </c>
       <c r="E2" t="n">
-        <v>2487797000</v>
+        <v>2468672000</v>
       </c>
       <c r="F2" t="n">
         <v>245552000</v>
@@ -659,7 +659,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,22 +668,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>151400000</v>
+        <v>185900000</v>
       </c>
       <c r="D3" t="n">
-        <v>2334</v>
+        <v>2336</v>
       </c>
       <c r="E3" t="n">
-        <v>3268954000</v>
+        <v>3272351000</v>
       </c>
       <c r="F3" t="n">
-        <v>386936000</v>
+        <v>384336000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>98700000</v>
+        <v>110100000</v>
       </c>
       <c r="D4" t="n">
-        <v>2170</v>
+        <v>2164</v>
       </c>
       <c r="E4" t="n">
-        <v>2634535000</v>
+        <v>2623585000</v>
       </c>
       <c r="F4" t="n">
-        <v>360885000</v>
+        <v>359435000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,13 +719,13 @@
         <v>86100000</v>
       </c>
       <c r="D5" t="n">
-        <v>2495</v>
+        <v>2480</v>
       </c>
       <c r="E5" t="n">
-        <v>3002652000</v>
+        <v>2982942000</v>
       </c>
       <c r="F5" t="n">
-        <v>503001000</v>
+        <v>501891000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -835,16 +835,16 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H2" t="n">
-        <v>546945000</v>
+        <v>542895000</v>
       </c>
       <c r="I2" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>39100000</v>
+        <v>19450000</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -885,28 +885,28 @@
         <v>482</v>
       </c>
       <c r="H3" t="n">
-        <v>519207000</v>
+        <v>517347000</v>
       </c>
       <c r="I3" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="J3" t="n">
-        <v>69100000</v>
+        <v>56420000</v>
       </c>
       <c r="K3" t="n">
         <v>194</v>
       </c>
       <c r="L3" t="n">
-        <v>182716000</v>
+        <v>182616000</v>
       </c>
       <c r="M3" t="n">
-        <v>35.19</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,31 +929,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H4" t="n">
-        <v>177870000</v>
+        <v>177220000</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>12270000</v>
+        <v>11820000</v>
       </c>
       <c r="K4" t="n">
         <v>106</v>
       </c>
       <c r="L4" t="n">
-        <v>131300000</v>
+        <v>131100000</v>
       </c>
       <c r="M4" t="n">
-        <v>73.81999999999999</v>
+        <v>73.98</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -976,16 +976,16 @@
         <v>48600000</v>
       </c>
       <c r="G5" t="n">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="H5" t="n">
-        <v>790710000</v>
+        <v>783110000</v>
       </c>
       <c r="I5" t="n">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="J5" t="n">
-        <v>187600000</v>
+        <v>150800000</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
@@ -994,13 +994,13 @@
         <v>27995000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1026,28 +1026,28 @@
         <v>527</v>
       </c>
       <c r="H6" t="n">
-        <v>464770000</v>
+        <v>459670000</v>
       </c>
       <c r="I6" t="n">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="J6" t="n">
-        <v>119900000</v>
+        <v>84400000</v>
       </c>
       <c r="K6" t="n">
         <v>145</v>
       </c>
       <c r="L6" t="n">
-        <v>114165000</v>
+        <v>113805000</v>
       </c>
       <c r="M6" t="n">
-        <v>24.56</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1070,10 +1070,10 @@
         <v>3600000</v>
       </c>
       <c r="G7" t="n">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="H7" t="n">
-        <v>503150000</v>
+        <v>502700000</v>
       </c>
       <c r="I7" t="n">
         <v>248</v>
@@ -1082,19 +1082,19 @@
         <v>195855000</v>
       </c>
       <c r="K7" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L7" t="n">
-        <v>46825000</v>
+        <v>46375000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.31</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1120,13 +1120,13 @@
         <v>376</v>
       </c>
       <c r="H8" t="n">
-        <v>360184000</v>
+        <v>356744000</v>
       </c>
       <c r="I8" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="J8" t="n">
-        <v>62455000</v>
+        <v>41845000</v>
       </c>
       <c r="K8" t="n">
         <v>161</v>
@@ -1135,13 +1135,13 @@
         <v>121510000</v>
       </c>
       <c r="M8" t="n">
-        <v>33.74</v>
+        <v>34.06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1188,7 +1188,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1211,16 +1211,16 @@
         <v>10800000</v>
       </c>
       <c r="G10" t="n">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="H10" t="n">
-        <v>527898000</v>
+        <v>525648000</v>
       </c>
       <c r="I10" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J10" t="n">
-        <v>58550000</v>
+        <v>52050000</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F11" t="n">
-        <v>61800000</v>
+        <v>73200000</v>
       </c>
       <c r="G11" t="n">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="H11" t="n">
-        <v>839158000</v>
+        <v>842598000</v>
       </c>
       <c r="I11" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
-        <v>62710000</v>
+        <v>22550000</v>
       </c>
       <c r="K11" t="n">
         <v>17</v>
@@ -1276,13 +1276,13 @@
         <v>26225000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1308,28 +1308,28 @@
         <v>359</v>
       </c>
       <c r="H12" t="n">
-        <v>401715000</v>
+        <v>398385000</v>
       </c>
       <c r="I12" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>26890000</v>
+        <v>6690000</v>
       </c>
       <c r="K12" t="n">
         <v>59</v>
       </c>
       <c r="L12" t="n">
-        <v>57305000</v>
+        <v>57055000</v>
       </c>
       <c r="M12" t="n">
-        <v>14.27</v>
+        <v>14.32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1355,28 +1355,28 @@
         <v>421</v>
       </c>
       <c r="H13" t="n">
-        <v>352295000</v>
+        <v>346925000</v>
       </c>
       <c r="I13" t="n">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="J13" t="n">
-        <v>75810000</v>
+        <v>44130000</v>
       </c>
       <c r="K13" t="n">
         <v>138</v>
       </c>
       <c r="L13" t="n">
-        <v>112085000</v>
+        <v>110885000</v>
       </c>
       <c r="M13" t="n">
-        <v>31.82</v>
+        <v>31.96</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1402,28 +1402,28 @@
         <v>562</v>
       </c>
       <c r="H14" t="n">
-        <v>729714000</v>
+        <v>722914000</v>
       </c>
       <c r="I14" t="n">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="J14" t="n">
-        <v>121565000</v>
+        <v>74115000</v>
       </c>
       <c r="K14" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="L14" t="n">
-        <v>72786000</v>
+        <v>70611000</v>
       </c>
       <c r="M14" t="n">
-        <v>9.970000000000001</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1437,25 +1437,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>24000000</v>
+        <v>36000000</v>
       </c>
       <c r="G15" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H15" t="n">
-        <v>539380000</v>
+        <v>548955000</v>
       </c>
       <c r="I15" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>62900000</v>
+        <v>44600000</v>
       </c>
       <c r="K15" t="n">
         <v>50</v>
@@ -1464,13 +1464,13 @@
         <v>87725000</v>
       </c>
       <c r="M15" t="n">
-        <v>16.26</v>
+        <v>15.98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1496,28 +1496,28 @@
         <v>323</v>
       </c>
       <c r="H16" t="n">
-        <v>386765000</v>
+        <v>384965000</v>
       </c>
       <c r="I16" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>31820000</v>
+        <v>25060000</v>
       </c>
       <c r="K16" t="n">
         <v>98</v>
       </c>
       <c r="L16" t="n">
-        <v>125825000</v>
+        <v>125400000</v>
       </c>
       <c r="M16" t="n">
-        <v>32.53</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1543,13 +1543,13 @@
         <v>580</v>
       </c>
       <c r="H17" t="n">
-        <v>957664000</v>
+        <v>947164000</v>
       </c>
       <c r="I17" t="n">
-        <v>194</v>
+        <v>145</v>
       </c>
       <c r="J17" t="n">
-        <v>303394000</v>
+        <v>249444000</v>
       </c>
       <c r="K17" t="n">
         <v>53</v>
@@ -1558,13 +1558,13 @@
         <v>42650000</v>
       </c>
       <c r="M17" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,25 +1578,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F18" t="n">
-        <v>47300000</v>
+        <v>69800000</v>
       </c>
       <c r="G18" t="n">
         <v>576</v>
       </c>
       <c r="H18" t="n">
-        <v>655431000</v>
+        <v>668353000</v>
       </c>
       <c r="I18" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J18" t="n">
-        <v>75192000</v>
+        <v>20200000</v>
       </c>
       <c r="K18" t="n">
         <v>61</v>
@@ -1605,13 +1605,13 @@
         <v>57950000</v>
       </c>
       <c r="M18" t="n">
-        <v>8.84</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1634,16 +1634,16 @@
         <v>66750000</v>
       </c>
       <c r="G19" t="n">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="H19" t="n">
-        <v>488105000</v>
+        <v>480915000</v>
       </c>
       <c r="I19" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>51775000</v>
+        <v>17175000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1684,13 +1684,13 @@
         <v>292</v>
       </c>
       <c r="H20" t="n">
-        <v>360775000</v>
+        <v>357775000</v>
       </c>
       <c r="I20" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>52125000</v>
+        <v>32825000</v>
       </c>
       <c r="K20" t="n">
         <v>62</v>
@@ -1699,13 +1699,13 @@
         <v>63370000</v>
       </c>
       <c r="M20" t="n">
-        <v>17.56</v>
+        <v>17.71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1731,13 +1731,13 @@
         <v>449</v>
       </c>
       <c r="H21" t="n">
-        <v>466837000</v>
+        <v>464037000</v>
       </c>
       <c r="I21" t="n">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="J21" t="n">
-        <v>143345000</v>
+        <v>118745000</v>
       </c>
       <c r="K21" t="n">
         <v>79</v>
@@ -1746,13 +1746,13 @@
         <v>87972000</v>
       </c>
       <c r="M21" t="n">
-        <v>18.84</v>
+        <v>18.96</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,25 +1766,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E22" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F22" t="n">
-        <v>72900000</v>
+        <v>79800000</v>
       </c>
       <c r="G22" t="n">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H22" t="n">
-        <v>774520000</v>
+        <v>771060000</v>
       </c>
       <c r="I22" t="n">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="J22" t="n">
-        <v>147110000</v>
+        <v>89120000</v>
       </c>
       <c r="K22" t="n">
         <v>34</v>
@@ -1793,13 +1793,13 @@
         <v>56975000</v>
       </c>
       <c r="M22" t="n">
-        <v>7.36</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1872,13 +1872,13 @@
         <v>250</v>
       </c>
       <c r="H24" t="n">
-        <v>327500000</v>
+        <v>324825000</v>
       </c>
       <c r="I24" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>45975000</v>
+        <v>30900000</v>
       </c>
       <c r="K24" t="n">
         <v>14</v>
@@ -1887,7 +1887,7 @@
         <v>8375000</v>
       </c>
       <c r="M24" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
     </row>
   </sheetData>
@@ -2192,10 +2192,10 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>151400000</v>
+        <v>185900000</v>
       </c>
       <c r="Q2" t="n">
-        <v>449821000</v>
+        <v>420968000</v>
       </c>
     </row>
     <row r="3">
@@ -2243,10 +2243,10 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>189750000</v>
+        <v>196650000</v>
       </c>
       <c r="Q3" t="n">
-        <v>285462000</v>
+        <v>263437000</v>
       </c>
     </row>
     <row r="4">
@@ -2297,7 +2297,7 @@
         <v>86100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>584494000</v>
+        <v>568804000</v>
       </c>
     </row>
     <row r="5">
@@ -2345,10 +2345,10 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>98700000</v>
+        <v>110100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>397825001</v>
+        <v>377995001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>568804000</v>
+        <v>514849000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>420968000</v>
+        <v>380559000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>377995001</v>
+        <v>357045001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>263437000</v>
+        <v>233447000</v>
       </c>
     </row>
   </sheetData>
@@ -517,73 +517,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>243100000</v>
+        <v>122220000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>199590000</v>
+        <v>106000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>141200000</v>
+        <v>63700000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>107500000</v>
+        <v>45500000</v>
       </c>
     </row>
   </sheetData>
@@ -635,97 +635,97 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>196650000</v>
+        <v>397200000</v>
       </c>
       <c r="D2" t="n">
-        <v>2040</v>
+        <v>2386</v>
       </c>
       <c r="E2" t="n">
-        <v>2468672000</v>
+        <v>3424022000</v>
       </c>
       <c r="F2" t="n">
-        <v>245552000</v>
+        <v>379486000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>185900000</v>
+        <v>388300000</v>
       </c>
       <c r="D3" t="n">
-        <v>2336</v>
+        <v>2551</v>
       </c>
       <c r="E3" t="n">
-        <v>3272351000</v>
+        <v>3184022000</v>
       </c>
       <c r="F3" t="n">
-        <v>384336000</v>
+        <v>498791000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>110100000</v>
+        <v>360700000</v>
       </c>
       <c r="D4" t="n">
-        <v>2164</v>
+        <v>2094</v>
       </c>
       <c r="E4" t="n">
-        <v>2623585000</v>
+        <v>2588607000</v>
       </c>
       <c r="F4" t="n">
-        <v>359435000</v>
+        <v>236552000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>86100000</v>
+        <v>320190000</v>
       </c>
       <c r="D5" t="n">
-        <v>2480</v>
+        <v>2219</v>
       </c>
       <c r="E5" t="n">
-        <v>2982942000</v>
+        <v>2791685000</v>
       </c>
       <c r="F5" t="n">
-        <v>501891000</v>
+        <v>356885000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2" t="n">
+        <v>65100000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>357</v>
+      </c>
+      <c r="H2" t="n">
+        <v>578675000</v>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
+      <c r="J2" t="n">
         <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>354</v>
-      </c>
-      <c r="H2" t="n">
-        <v>542895000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J2" t="n">
-        <v>19450000</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +873,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="F3" t="n">
-        <v>3000000</v>
+        <v>59400000</v>
       </c>
       <c r="G3" t="n">
-        <v>482</v>
+        <v>512</v>
       </c>
       <c r="H3" t="n">
-        <v>517347000</v>
+        <v>562967000</v>
       </c>
       <c r="I3" t="n">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="J3" t="n">
-        <v>56420000</v>
+        <v>23970000</v>
       </c>
       <c r="K3" t="n">
         <v>194</v>
       </c>
       <c r="L3" t="n">
-        <v>182616000</v>
+        <v>182166000</v>
       </c>
       <c r="M3" t="n">
-        <v>35.3</v>
+        <v>32.36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -932,28 +932,28 @@
         <v>177</v>
       </c>
       <c r="H4" t="n">
-        <v>177220000</v>
+        <v>176070000</v>
       </c>
       <c r="I4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>11820000</v>
+        <v>7320000</v>
       </c>
       <c r="K4" t="n">
         <v>106</v>
       </c>
       <c r="L4" t="n">
-        <v>131100000</v>
+        <v>130850000</v>
       </c>
       <c r="M4" t="n">
-        <v>73.98</v>
+        <v>74.31999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,25 +967,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F5" t="n">
-        <v>48600000</v>
+        <v>126300000</v>
       </c>
       <c r="G5" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="H5" t="n">
-        <v>783110000</v>
+        <v>827585000</v>
       </c>
       <c r="I5" t="n">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="J5" t="n">
-        <v>150800000</v>
+        <v>15100000</v>
       </c>
       <c r="K5" t="n">
         <v>18</v>
@@ -994,13 +994,13 @@
         <v>27995000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n">
-        <v>30900000</v>
+        <v>54500000</v>
       </c>
       <c r="G6" t="n">
-        <v>527</v>
+        <v>543</v>
       </c>
       <c r="H6" t="n">
-        <v>459670000</v>
+        <v>476415000</v>
       </c>
       <c r="I6" t="n">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="J6" t="n">
-        <v>84400000</v>
+        <v>56260000</v>
       </c>
       <c r="K6" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="L6" t="n">
-        <v>113805000</v>
+        <v>111405000</v>
       </c>
       <c r="M6" t="n">
-        <v>24.76</v>
+        <v>23.38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,25 +1061,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
-        <v>3600000</v>
+        <v>83000000</v>
       </c>
       <c r="G7" t="n">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="H7" t="n">
-        <v>502700000</v>
+        <v>562310000</v>
       </c>
       <c r="I7" t="n">
-        <v>248</v>
+        <v>131</v>
       </c>
       <c r="J7" t="n">
-        <v>195855000</v>
+        <v>117380000</v>
       </c>
       <c r="K7" t="n">
         <v>36</v>
@@ -1088,13 +1088,13 @@
         <v>46375000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.23</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,40 +1108,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
-        <v>5400000</v>
+        <v>22200000</v>
       </c>
       <c r="G8" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H8" t="n">
-        <v>356744000</v>
+        <v>365944000</v>
       </c>
       <c r="I8" t="n">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="J8" t="n">
-        <v>41845000</v>
+        <v>19100000</v>
       </c>
       <c r="K8" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="L8" t="n">
-        <v>121510000</v>
+        <v>119110000</v>
       </c>
       <c r="M8" t="n">
-        <v>34.06</v>
+        <v>32.55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>42600000</v>
       </c>
       <c r="G9" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="H9" t="n">
-        <v>153285000</v>
+        <v>195885000</v>
       </c>
       <c r="I9" t="n">
         <v>2</v>
@@ -1182,13 +1182,13 @@
         <v>42210000</v>
       </c>
       <c r="M9" t="n">
-        <v>27.54</v>
+        <v>21.55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>10800000</v>
+        <v>46740000</v>
       </c>
       <c r="G10" t="n">
         <v>402</v>
       </c>
       <c r="H10" t="n">
-        <v>525648000</v>
+        <v>548628000</v>
       </c>
       <c r="I10" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>52050000</v>
+        <v>11400000</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -1229,13 +1229,13 @@
         <v>1550000</v>
       </c>
       <c r="M10" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,40 +1249,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F11" t="n">
-        <v>73200000</v>
+        <v>123450000</v>
       </c>
       <c r="G11" t="n">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="H11" t="n">
-        <v>842598000</v>
+        <v>876798000</v>
       </c>
       <c r="I11" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>22550000</v>
+        <v>3300000</v>
       </c>
       <c r="K11" t="n">
         <v>17</v>
       </c>
       <c r="L11" t="n">
-        <v>26225000</v>
+        <v>26075000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.11</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,25 +1296,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F12" t="n">
-        <v>20700000</v>
+        <v>61500000</v>
       </c>
       <c r="G12" t="n">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="H12" t="n">
-        <v>398385000</v>
+        <v>437075000</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>6690000</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>59</v>
@@ -1323,13 +1323,13 @@
         <v>57055000</v>
       </c>
       <c r="M12" t="n">
-        <v>14.32</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,25 +1343,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>23700000</v>
       </c>
       <c r="G13" t="n">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="H13" t="n">
-        <v>346925000</v>
+        <v>367355000</v>
       </c>
       <c r="I13" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="J13" t="n">
-        <v>44130000</v>
+        <v>34440000</v>
       </c>
       <c r="K13" t="n">
         <v>138</v>
@@ -1370,13 +1370,13 @@
         <v>110885000</v>
       </c>
       <c r="M13" t="n">
-        <v>31.96</v>
+        <v>30.18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,40 +1390,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F14" t="n">
-        <v>56400000</v>
+        <v>86400000</v>
       </c>
       <c r="G14" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H14" t="n">
-        <v>722914000</v>
+        <v>735755000</v>
       </c>
       <c r="I14" t="n">
+        <v>33</v>
+      </c>
+      <c r="J14" t="n">
+        <v>19750000</v>
+      </c>
+      <c r="K14" t="n">
         <v>84</v>
       </c>
-      <c r="J14" t="n">
-        <v>74115000</v>
-      </c>
-      <c r="K14" t="n">
-        <v>87</v>
-      </c>
       <c r="L14" t="n">
-        <v>70611000</v>
+        <v>68211000</v>
       </c>
       <c r="M14" t="n">
-        <v>9.77</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1437,40 +1437,40 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F15" t="n">
-        <v>36000000</v>
+        <v>112800000</v>
       </c>
       <c r="G15" t="n">
-        <v>295</v>
+        <v>320</v>
       </c>
       <c r="H15" t="n">
-        <v>548955000</v>
+        <v>619115000</v>
       </c>
       <c r="I15" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>44600000</v>
+        <v>12100000</v>
       </c>
       <c r="K15" t="n">
         <v>50</v>
       </c>
       <c r="L15" t="n">
-        <v>87725000</v>
+        <v>86225000</v>
       </c>
       <c r="M15" t="n">
-        <v>15.98</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1496,28 +1496,28 @@
         <v>323</v>
       </c>
       <c r="H16" t="n">
-        <v>384965000</v>
+        <v>379285000</v>
       </c>
       <c r="I16" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>25060000</v>
+        <v>3680000</v>
       </c>
       <c r="K16" t="n">
         <v>98</v>
       </c>
       <c r="L16" t="n">
-        <v>125400000</v>
+        <v>124450000</v>
       </c>
       <c r="M16" t="n">
-        <v>32.57</v>
+        <v>32.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,25 +1531,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F17" t="n">
-        <v>23700000</v>
+        <v>90200000</v>
       </c>
       <c r="G17" t="n">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="H17" t="n">
-        <v>947164000</v>
+        <v>990639000</v>
       </c>
       <c r="I17" t="n">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="J17" t="n">
-        <v>249444000</v>
+        <v>154544000</v>
       </c>
       <c r="K17" t="n">
         <v>53</v>
@@ -1558,13 +1558,13 @@
         <v>42650000</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,25 +1578,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E18" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="F18" t="n">
-        <v>69800000</v>
+        <v>107800000</v>
       </c>
       <c r="G18" t="n">
-        <v>576</v>
+        <v>587</v>
       </c>
       <c r="H18" t="n">
-        <v>668353000</v>
+        <v>699228000</v>
       </c>
       <c r="I18" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>20200000</v>
+        <v>17300000</v>
       </c>
       <c r="K18" t="n">
         <v>61</v>
@@ -1605,13 +1605,13 @@
         <v>57950000</v>
       </c>
       <c r="M18" t="n">
-        <v>8.67</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1625,25 +1625,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F19" t="n">
-        <v>66750000</v>
+        <v>80750000</v>
       </c>
       <c r="G19" t="n">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="H19" t="n">
-        <v>480915000</v>
+        <v>488640000</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>17175000</v>
+        <v>525000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1672,25 +1672,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F20" t="n">
-        <v>4500000</v>
+        <v>29750000</v>
       </c>
       <c r="G20" t="n">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="H20" t="n">
-        <v>357775000</v>
+        <v>375050000</v>
       </c>
       <c r="I20" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="J20" t="n">
-        <v>32825000</v>
+        <v>17400000</v>
       </c>
       <c r="K20" t="n">
         <v>62</v>
@@ -1699,13 +1699,13 @@
         <v>63370000</v>
       </c>
       <c r="M20" t="n">
-        <v>17.71</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,25 +1719,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="F21" t="n">
-        <v>8100000</v>
+        <v>61800000</v>
       </c>
       <c r="G21" t="n">
-        <v>449</v>
+        <v>478</v>
       </c>
       <c r="H21" t="n">
-        <v>464037000</v>
+        <v>504052000</v>
       </c>
       <c r="I21" t="n">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="J21" t="n">
-        <v>118745000</v>
+        <v>54400000</v>
       </c>
       <c r="K21" t="n">
         <v>79</v>
@@ -1746,13 +1746,13 @@
         <v>87972000</v>
       </c>
       <c r="M21" t="n">
-        <v>18.96</v>
+        <v>17.45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,40 +1766,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E22" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F22" t="n">
-        <v>79800000</v>
+        <v>89700000</v>
       </c>
       <c r="G22" t="n">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="H22" t="n">
-        <v>771060000</v>
+        <v>767680000</v>
       </c>
       <c r="I22" t="n">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>89120000</v>
+        <v>26600000</v>
       </c>
       <c r="K22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L22" t="n">
-        <v>56975000</v>
+        <v>48975000</v>
       </c>
       <c r="M22" t="n">
-        <v>7.39</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1813,19 +1813,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F23" t="n">
-        <v>25500000</v>
+        <v>41500000</v>
       </c>
       <c r="G23" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H23" t="n">
-        <v>70060000</v>
+        <v>85060000</v>
       </c>
       <c r="I23" t="n">
         <v>2</v>
@@ -1834,19 +1834,19 @@
         <v>250000</v>
       </c>
       <c r="K23" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L23" t="n">
-        <v>28860000</v>
+        <v>27860000</v>
       </c>
       <c r="M23" t="n">
-        <v>41.19</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,25 +1860,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F24" t="n">
-        <v>12000000</v>
+        <v>57200000</v>
       </c>
       <c r="G24" t="n">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="H24" t="n">
-        <v>324825000</v>
+        <v>368125000</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>30900000</v>
+        <v>28650000</v>
       </c>
       <c r="K24" t="n">
         <v>14</v>
@@ -1887,7 +1887,7 @@
         <v>8375000</v>
       </c>
       <c r="M24" t="n">
-        <v>2.58</v>
+        <v>2.28</v>
       </c>
     </row>
   </sheetData>
@@ -2192,10 +2192,10 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>185900000</v>
+        <v>397200000</v>
       </c>
       <c r="Q2" t="n">
-        <v>420968000</v>
+        <v>380559000</v>
       </c>
     </row>
     <row r="3">
@@ -2243,10 +2243,10 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>196650000</v>
+        <v>360700000</v>
       </c>
       <c r="Q3" t="n">
-        <v>263437000</v>
+        <v>233447000</v>
       </c>
     </row>
     <row r="4">
@@ -2294,10 +2294,10 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>86100000</v>
+        <v>388300000</v>
       </c>
       <c r="Q4" t="n">
-        <v>568804000</v>
+        <v>514849000</v>
       </c>
     </row>
     <row r="5">
@@ -2345,10 +2345,10 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>110100000</v>
+        <v>320190000</v>
       </c>
       <c r="Q5" t="n">
-        <v>377995001</v>
+        <v>357045001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>514849000</v>
+        <v>510149000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>380559000</v>
+        <v>376029000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>357045001</v>
+        <v>348895001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>233447000</v>
+        <v>232097000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,16 +526,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>122220000</v>
+        <v>93120000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -544,46 +544,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>106000000</v>
+        <v>89800000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>63700000</v>
+        <v>65000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>45500000</v>
+        <v>42000000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,22 +644,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>397200000</v>
+        <v>417000000</v>
       </c>
       <c r="D2" t="n">
-        <v>2386</v>
+        <v>2471</v>
       </c>
       <c r="E2" t="n">
-        <v>3424022000</v>
+        <v>3502130400</v>
       </c>
       <c r="F2" t="n">
-        <v>379486000</v>
+        <v>438174400</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,22 +668,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>388300000</v>
+        <v>403000000</v>
       </c>
       <c r="D3" t="n">
-        <v>2551</v>
+        <v>2623</v>
       </c>
       <c r="E3" t="n">
-        <v>3184022000</v>
+        <v>3239908600.6</v>
       </c>
       <c r="F3" t="n">
-        <v>498791000</v>
+        <v>548427600.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>360700000</v>
+        <v>401350000</v>
       </c>
       <c r="D4" t="n">
-        <v>2094</v>
+        <v>2213</v>
       </c>
       <c r="E4" t="n">
-        <v>2588607000</v>
+        <v>2683889160</v>
       </c>
       <c r="F4" t="n">
-        <v>236552000</v>
+        <v>297784160</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>320190000</v>
+        <v>370890000</v>
       </c>
       <c r="D5" t="n">
-        <v>2219</v>
+        <v>2353</v>
       </c>
       <c r="E5" t="n">
-        <v>2791685000</v>
+        <v>2896134840</v>
       </c>
       <c r="F5" t="n">
-        <v>356885000</v>
+        <v>419394840</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>65100000</v>
+        <v>69900000</v>
       </c>
       <c r="G2" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="H2" t="n">
-        <v>578675000</v>
+        <v>583915200</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -847,19 +847,19 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3940200</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +873,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F3" t="n">
-        <v>59400000</v>
+        <v>65700000</v>
       </c>
       <c r="G3" t="n">
-        <v>512</v>
+        <v>527</v>
       </c>
       <c r="H3" t="n">
-        <v>562967000</v>
+        <v>573490520</v>
       </c>
       <c r="I3" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J3" t="n">
-        <v>23970000</v>
+        <v>16530000</v>
       </c>
       <c r="K3" t="n">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="L3" t="n">
-        <v>182166000</v>
+        <v>188219520</v>
       </c>
       <c r="M3" t="n">
-        <v>32.36</v>
+        <v>32.82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,10 +929,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="H4" t="n">
-        <v>176070000</v>
+        <v>209680480.6</v>
       </c>
       <c r="I4" t="n">
         <v>12</v>
@@ -941,19 +941,19 @@
         <v>7320000</v>
       </c>
       <c r="K4" t="n">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="L4" t="n">
-        <v>130850000</v>
+        <v>164460480.6</v>
       </c>
       <c r="M4" t="n">
-        <v>74.31999999999999</v>
+        <v>78.43000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,40 +967,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F5" t="n">
-        <v>126300000</v>
+        <v>129900000</v>
       </c>
       <c r="G5" t="n">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="H5" t="n">
-        <v>827585000</v>
+        <v>832826600</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>15100000</v>
+        <v>7000000</v>
       </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="L5" t="n">
-        <v>27995000</v>
+        <v>31136600</v>
       </c>
       <c r="M5" t="n">
-        <v>3.38</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1026,13 +1026,13 @@
         <v>543</v>
       </c>
       <c r="H6" t="n">
-        <v>476415000</v>
+        <v>474795000</v>
       </c>
       <c r="I6" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="J6" t="n">
-        <v>56260000</v>
+        <v>48340000</v>
       </c>
       <c r="K6" t="n">
         <v>142</v>
@@ -1041,13 +1041,13 @@
         <v>111405000</v>
       </c>
       <c r="M6" t="n">
-        <v>23.38</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1070,10 +1070,10 @@
         <v>83000000</v>
       </c>
       <c r="G7" t="n">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="H7" t="n">
-        <v>562310000</v>
+        <v>565200800</v>
       </c>
       <c r="I7" t="n">
         <v>131</v>
@@ -1082,19 +1082,19 @@
         <v>117380000</v>
       </c>
       <c r="K7" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L7" t="n">
-        <v>46375000</v>
+        <v>49265800</v>
       </c>
       <c r="M7" t="n">
-        <v>8.25</v>
+        <v>8.720000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,25 +1108,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F8" t="n">
-        <v>22200000</v>
+        <v>36600000</v>
       </c>
       <c r="G8" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H8" t="n">
-        <v>365944000</v>
+        <v>377974000</v>
       </c>
       <c r="I8" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J8" t="n">
-        <v>19100000</v>
+        <v>14300000</v>
       </c>
       <c r="K8" t="n">
         <v>158</v>
@@ -1135,13 +1135,13 @@
         <v>119110000</v>
       </c>
       <c r="M8" t="n">
-        <v>32.55</v>
+        <v>31.51</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F9" t="n">
-        <v>42600000</v>
+        <v>64200000</v>
       </c>
       <c r="G9" t="n">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="H9" t="n">
-        <v>195885000</v>
+        <v>235966320</v>
       </c>
       <c r="I9" t="n">
         <v>2</v>
@@ -1176,19 +1176,19 @@
         <v>3600000</v>
       </c>
       <c r="K9" t="n">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="L9" t="n">
-        <v>42210000</v>
+        <v>60691320</v>
       </c>
       <c r="M9" t="n">
-        <v>21.55</v>
+        <v>25.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1211,31 +1211,31 @@
         <v>46740000</v>
       </c>
       <c r="G10" t="n">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="H10" t="n">
-        <v>548628000</v>
+        <v>552488200</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>11400000</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
-        <v>1550000</v>
+        <v>6810200</v>
       </c>
       <c r="M10" t="n">
-        <v>0.28</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1261,13 +1261,13 @@
         <v>479</v>
       </c>
       <c r="H11" t="n">
-        <v>876798000</v>
+        <v>875948000</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3300000</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>17</v>
@@ -1276,13 +1276,13 @@
         <v>26075000</v>
       </c>
       <c r="M11" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1305,10 +1305,10 @@
         <v>61500000</v>
       </c>
       <c r="G12" t="n">
-        <v>380</v>
+        <v>422</v>
       </c>
       <c r="H12" t="n">
-        <v>437075000</v>
+        <v>456865520</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1317,19 +1317,19 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="L12" t="n">
-        <v>57055000</v>
+        <v>77595520</v>
       </c>
       <c r="M12" t="n">
-        <v>13.05</v>
+        <v>16.98</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,40 +1343,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F13" t="n">
-        <v>23700000</v>
+        <v>38400000</v>
       </c>
       <c r="G13" t="n">
-        <v>430</v>
+        <v>463</v>
       </c>
       <c r="H13" t="n">
-        <v>367355000</v>
+        <v>396892800</v>
       </c>
       <c r="I13" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="J13" t="n">
-        <v>34440000</v>
+        <v>18570000</v>
       </c>
       <c r="K13" t="n">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="L13" t="n">
-        <v>110885000</v>
+        <v>129112800</v>
       </c>
       <c r="M13" t="n">
-        <v>30.18</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1399,31 +1399,31 @@
         <v>86400000</v>
       </c>
       <c r="G14" t="n">
-        <v>561</v>
+        <v>593</v>
       </c>
       <c r="H14" t="n">
-        <v>735755000</v>
+        <v>757812080</v>
       </c>
       <c r="I14" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>19750000</v>
+        <v>17950000</v>
       </c>
       <c r="K14" t="n">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="L14" t="n">
-        <v>68211000</v>
+        <v>92068080</v>
       </c>
       <c r="M14" t="n">
-        <v>9.27</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1446,31 +1446,31 @@
         <v>112800000</v>
       </c>
       <c r="G15" t="n">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="H15" t="n">
-        <v>619115000</v>
+        <v>629664440</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J15" t="n">
-        <v>12100000</v>
+        <v>19300000</v>
       </c>
       <c r="K15" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="L15" t="n">
-        <v>86225000</v>
+        <v>91674440</v>
       </c>
       <c r="M15" t="n">
-        <v>13.93</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1493,31 +1493,31 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>323</v>
+        <v>357</v>
       </c>
       <c r="H16" t="n">
-        <v>379285000</v>
+        <v>404866880</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>3680000</v>
+        <v>750000</v>
       </c>
       <c r="K16" t="n">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="L16" t="n">
-        <v>124450000</v>
+        <v>150861880</v>
       </c>
       <c r="M16" t="n">
-        <v>32.81</v>
+        <v>37.26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,25 +1531,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F17" t="n">
-        <v>90200000</v>
+        <v>94700000</v>
       </c>
       <c r="G17" t="n">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="H17" t="n">
-        <v>990639000</v>
+        <v>993539000</v>
       </c>
       <c r="I17" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="J17" t="n">
-        <v>154544000</v>
+        <v>151094000</v>
       </c>
       <c r="K17" t="n">
         <v>53</v>
@@ -1558,13 +1558,13 @@
         <v>42650000</v>
       </c>
       <c r="M17" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,19 +1578,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E18" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F18" t="n">
-        <v>107800000</v>
+        <v>123100000</v>
       </c>
       <c r="G18" t="n">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="H18" t="n">
-        <v>699228000</v>
+        <v>716248000</v>
       </c>
       <c r="I18" t="n">
         <v>8</v>
@@ -1599,19 +1599,19 @@
         <v>17300000</v>
       </c>
       <c r="K18" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="L18" t="n">
-        <v>57950000</v>
+        <v>60920000</v>
       </c>
       <c r="M18" t="n">
-        <v>8.289999999999999</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1634,10 +1634,10 @@
         <v>80750000</v>
       </c>
       <c r="G19" t="n">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="H19" t="n">
-        <v>488640000</v>
+        <v>488086000</v>
       </c>
       <c r="I19" t="n">
         <v>3</v>
@@ -1646,19 +1646,19 @@
         <v>525000</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>396000</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1672,19 +1672,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E20" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F20" t="n">
-        <v>29750000</v>
+        <v>55500000</v>
       </c>
       <c r="G20" t="n">
-        <v>298</v>
+        <v>347</v>
       </c>
       <c r="H20" t="n">
-        <v>375050000</v>
+        <v>411027360</v>
       </c>
       <c r="I20" t="n">
         <v>15</v>
@@ -1693,19 +1693,19 @@
         <v>17400000</v>
       </c>
       <c r="K20" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="L20" t="n">
-        <v>63370000</v>
+        <v>73597360</v>
       </c>
       <c r="M20" t="n">
-        <v>16.9</v>
+        <v>17.91</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1728,10 +1728,10 @@
         <v>61800000</v>
       </c>
       <c r="G21" t="n">
-        <v>478</v>
+        <v>506</v>
       </c>
       <c r="H21" t="n">
-        <v>504052000</v>
+        <v>535425200</v>
       </c>
       <c r="I21" t="n">
         <v>67</v>
@@ -1740,19 +1740,19 @@
         <v>54400000</v>
       </c>
       <c r="K21" t="n">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="L21" t="n">
-        <v>87972000</v>
+        <v>119995200</v>
       </c>
       <c r="M21" t="n">
-        <v>17.45</v>
+        <v>22.41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1775,31 +1775,31 @@
         <v>89700000</v>
       </c>
       <c r="G22" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H22" t="n">
-        <v>767680000</v>
+        <v>766918000</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>26600000</v>
+        <v>24200000</v>
       </c>
       <c r="K22" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L22" t="n">
-        <v>48975000</v>
+        <v>51813000</v>
       </c>
       <c r="M22" t="n">
-        <v>6.38</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1822,10 +1822,10 @@
         <v>41500000</v>
       </c>
       <c r="G23" t="n">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="H23" t="n">
-        <v>85060000</v>
+        <v>95263600</v>
       </c>
       <c r="I23" t="n">
         <v>2</v>
@@ -1834,19 +1834,19 @@
         <v>250000</v>
       </c>
       <c r="K23" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="L23" t="n">
-        <v>27860000</v>
+        <v>38063600</v>
       </c>
       <c r="M23" t="n">
-        <v>32.75</v>
+        <v>39.96</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,34 +1860,34 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F24" t="n">
-        <v>57200000</v>
+        <v>72100000</v>
       </c>
       <c r="G24" t="n">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="H24" t="n">
-        <v>368125000</v>
+        <v>387169000</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J24" t="n">
-        <v>28650000</v>
+        <v>25650000</v>
       </c>
       <c r="K24" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="L24" t="n">
-        <v>8375000</v>
+        <v>13919000</v>
       </c>
       <c r="M24" t="n">
-        <v>2.28</v>
+        <v>3.6</v>
       </c>
     </row>
   </sheetData>
@@ -2192,10 +2192,10 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>397200000</v>
+        <v>417000000</v>
       </c>
       <c r="Q2" t="n">
-        <v>380559000</v>
+        <v>376029000</v>
       </c>
     </row>
     <row r="3">
@@ -2243,10 +2243,10 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>360700000</v>
+        <v>401350000</v>
       </c>
       <c r="Q3" t="n">
-        <v>233447000</v>
+        <v>232097000</v>
       </c>
     </row>
     <row r="4">
@@ -2294,10 +2294,10 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>388300000</v>
+        <v>403000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>514849000</v>
+        <v>510149000</v>
       </c>
     </row>
     <row r="5">
@@ -2345,10 +2345,10 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>320190000</v>
+        <v>370890000</v>
       </c>
       <c r="Q5" t="n">
-        <v>357045001</v>
+        <v>348895001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>499089000</v>
+        <v>633489000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>359094000</v>
+        <v>511328000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>348535001</v>
+        <v>438938001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>230472000</v>
+        <v>334632000</v>
       </c>
     </row>
   </sheetData>
@@ -517,43 +517,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>89800000</v>
+        <v>70200000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>87120000</v>
+        <v>43100000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -562,28 +562,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>61100000</v>
+        <v>41600000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>30000000</v>
+        <v>30900000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,88 +644,88 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>435900000</v>
+        <v>157100000</v>
       </c>
       <c r="D2" t="n">
-        <v>2385</v>
+        <v>2397</v>
       </c>
       <c r="E2" t="n">
-        <v>3411807000</v>
+        <v>3365966000</v>
       </c>
       <c r="F2" t="n">
-        <v>363786000</v>
+        <v>457586000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>424900000</v>
+        <v>75400000</v>
       </c>
       <c r="D3" t="n">
-        <v>2561</v>
+        <v>2113</v>
       </c>
       <c r="E3" t="n">
-        <v>3197012000</v>
+        <v>2531912000</v>
       </c>
       <c r="F3" t="n">
-        <v>497541000</v>
+        <v>302397000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>423850000</v>
+        <v>63420000</v>
       </c>
       <c r="D4" t="n">
-        <v>2137</v>
+        <v>2231</v>
       </c>
       <c r="E4" t="n">
-        <v>2637972000</v>
+        <v>2749689000</v>
       </c>
       <c r="F4" t="n">
-        <v>236552000</v>
+        <v>371655000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>397290000</v>
+        <v>60900000</v>
       </c>
       <c r="D5" t="n">
-        <v>2241</v>
+        <v>2530</v>
       </c>
       <c r="E5" t="n">
-        <v>2855545000</v>
+        <v>3087146000</v>
       </c>
       <c r="F5" t="n">
-        <v>353145000</v>
+        <v>561101000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>91800000</v>
+        <v>4500000</v>
       </c>
       <c r="G2" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H2" t="n">
-        <v>601500000</v>
+        <v>568620000</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>161875000</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +873,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>65700000</v>
+        <v>6000000</v>
       </c>
       <c r="G3" t="n">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="H3" t="n">
-        <v>566062000</v>
+        <v>550804000</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>148</v>
       </c>
       <c r="J3" t="n">
-        <v>8780000</v>
+        <v>159635000</v>
       </c>
       <c r="K3" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="L3" t="n">
-        <v>182166000</v>
+        <v>183971000</v>
       </c>
       <c r="M3" t="n">
-        <v>32.18</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,31 +929,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H4" t="n">
-        <v>174070000</v>
+        <v>163750000</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="J4" t="n">
-        <v>2820000</v>
+        <v>18210000</v>
       </c>
       <c r="K4" t="n">
         <v>106</v>
       </c>
       <c r="L4" t="n">
-        <v>129600000</v>
+        <v>128040000</v>
       </c>
       <c r="M4" t="n">
-        <v>74.45</v>
+        <v>78.19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,40 +967,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>129900000</v>
+        <v>34200000</v>
       </c>
       <c r="G5" t="n">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="H5" t="n">
-        <v>827860000</v>
+        <v>809955000</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>186</v>
       </c>
       <c r="J5" t="n">
-        <v>1400000</v>
+        <v>324115000</v>
       </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="L5" t="n">
-        <v>27995000</v>
+        <v>43545000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.38</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>54500000</v>
+        <v>3000000</v>
       </c>
       <c r="G6" t="n">
-        <v>543</v>
+        <v>528</v>
       </c>
       <c r="H6" t="n">
-        <v>473415000</v>
+        <v>448927000</v>
       </c>
       <c r="I6" t="n">
-        <v>57</v>
+        <v>213</v>
       </c>
       <c r="J6" t="n">
-        <v>40060000</v>
+        <v>165502000</v>
       </c>
       <c r="K6" t="n">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="L6" t="n">
-        <v>111405000</v>
+        <v>120985000</v>
       </c>
       <c r="M6" t="n">
-        <v>23.53</v>
+        <v>26.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,40 +1061,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>83000000</v>
+        <v>13200000</v>
       </c>
       <c r="G7" t="n">
-        <v>515</v>
+        <v>497</v>
       </c>
       <c r="H7" t="n">
-        <v>554105000</v>
+        <v>545090000</v>
       </c>
       <c r="I7" t="n">
-        <v>95</v>
+        <v>344</v>
       </c>
       <c r="J7" t="n">
-        <v>63170000</v>
+        <v>320310000</v>
       </c>
       <c r="K7" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="L7" t="n">
-        <v>46375000</v>
+        <v>84560000</v>
       </c>
       <c r="M7" t="n">
-        <v>8.369999999999999</v>
+        <v>15.51</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,40 +1108,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>45000000</v>
+        <v>3600000</v>
       </c>
       <c r="G8" t="n">
         <v>383</v>
       </c>
       <c r="H8" t="n">
-        <v>386374000</v>
+        <v>377824000</v>
       </c>
       <c r="I8" t="n">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="J8" t="n">
-        <v>14300000</v>
+        <v>110799000</v>
       </c>
       <c r="K8" t="n">
         <v>158</v>
       </c>
       <c r="L8" t="n">
-        <v>119110000</v>
+        <v>118640000</v>
       </c>
       <c r="M8" t="n">
-        <v>30.83</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1155,40 +1155,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>64200000</v>
+        <v>10320000</v>
       </c>
       <c r="G9" t="n">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="H9" t="n">
-        <v>217485000</v>
+        <v>233915000</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="J9" t="n">
-        <v>3600000</v>
+        <v>62370000</v>
       </c>
       <c r="K9" t="n">
         <v>53</v>
       </c>
       <c r="L9" t="n">
-        <v>42210000</v>
+        <v>40590000</v>
       </c>
       <c r="M9" t="n">
-        <v>19.41</v>
+        <v>17.35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,40 +1202,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>46740000</v>
+        <v>12600000</v>
       </c>
       <c r="G10" t="n">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="H10" t="n">
-        <v>546528000</v>
+        <v>511595000</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>194760000</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L10" t="n">
-        <v>1550000</v>
+        <v>16850000</v>
       </c>
       <c r="M10" t="n">
-        <v>0.28</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,25 +1249,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>123450000</v>
+        <v>36900000</v>
       </c>
       <c r="G11" t="n">
         <v>479</v>
       </c>
       <c r="H11" t="n">
-        <v>874948000</v>
+        <v>841164000</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>239275000</v>
       </c>
       <c r="K11" t="n">
         <v>17</v>
@@ -1276,13 +1276,13 @@
         <v>26075000</v>
       </c>
       <c r="M11" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,40 +1296,40 @@
         </is>
       </c>
       <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>372</v>
+      </c>
+      <c r="H12" t="n">
+        <v>400071000</v>
+      </c>
+      <c r="I12" t="n">
+        <v>96</v>
+      </c>
+      <c r="J12" t="n">
+        <v>90160000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>56</v>
+      </c>
+      <c r="L12" t="n">
+        <v>56005000</v>
+      </c>
+      <c r="M12" t="n">
         <v>14</v>
-      </c>
-      <c r="E12" t="n">
-        <v>41</v>
-      </c>
-      <c r="F12" t="n">
-        <v>61500000</v>
-      </c>
-      <c r="G12" t="n">
-        <v>380</v>
-      </c>
-      <c r="H12" t="n">
-        <v>436325000</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>59</v>
-      </c>
-      <c r="L12" t="n">
-        <v>57055000</v>
-      </c>
-      <c r="M12" t="n">
-        <v>13.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,40 +1343,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>56400000</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H13" t="n">
-        <v>393885000</v>
+        <v>385120000</v>
       </c>
       <c r="I13" t="n">
-        <v>42</v>
+        <v>181</v>
       </c>
       <c r="J13" t="n">
-        <v>18930000</v>
+        <v>128895000</v>
       </c>
       <c r="K13" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="L13" t="n">
-        <v>107145000</v>
+        <v>113495000</v>
       </c>
       <c r="M13" t="n">
-        <v>27.2</v>
+        <v>29.47</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,40 +1390,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F14" t="n">
-        <v>86400000</v>
+        <v>64200000</v>
       </c>
       <c r="G14" t="n">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="H14" t="n">
-        <v>720945000</v>
+        <v>737051000</v>
       </c>
       <c r="I14" t="n">
-        <v>30</v>
+        <v>189</v>
       </c>
       <c r="J14" t="n">
-        <v>20830000</v>
+        <v>226966000</v>
       </c>
       <c r="K14" t="n">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="L14" t="n">
-        <v>62961000</v>
+        <v>77356000</v>
       </c>
       <c r="M14" t="n">
-        <v>8.73</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1437,40 +1437,40 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>112800000</v>
+        <v>31200000</v>
       </c>
       <c r="G15" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H15" t="n">
-        <v>610415000</v>
+        <v>610810000</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="J15" t="n">
-        <v>11300000</v>
+        <v>141255000</v>
       </c>
       <c r="K15" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="L15" t="n">
-        <v>77575000</v>
+        <v>97975000</v>
       </c>
       <c r="M15" t="n">
-        <v>12.71</v>
+        <v>16.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1484,40 +1484,40 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>21100000</v>
       </c>
       <c r="G16" t="n">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="H16" t="n">
-        <v>377755000</v>
+        <v>376240000</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="J16" t="n">
-        <v>750000</v>
+        <v>92300000</v>
       </c>
       <c r="K16" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="L16" t="n">
-        <v>124450000</v>
+        <v>133980000</v>
       </c>
       <c r="M16" t="n">
-        <v>32.94</v>
+        <v>35.61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,40 +1531,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>113600000</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="H17" t="n">
-        <v>992814000</v>
+        <v>940112000</v>
       </c>
       <c r="I17" t="n">
-        <v>36</v>
+        <v>275</v>
       </c>
       <c r="J17" t="n">
-        <v>57994000</v>
+        <v>417296000</v>
       </c>
       <c r="K17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="L17" t="n">
-        <v>40850000</v>
+        <v>84425000</v>
       </c>
       <c r="M17" t="n">
-        <v>4.11</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,40 +1578,40 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="F18" t="n">
-        <v>123100000</v>
+        <v>40600000</v>
       </c>
       <c r="G18" t="n">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="H18" t="n">
-        <v>709878000</v>
+        <v>701753000</v>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>214</v>
       </c>
       <c r="J18" t="n">
-        <v>11250000</v>
+        <v>248653000</v>
       </c>
       <c r="K18" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="L18" t="n">
-        <v>57950000</v>
+        <v>63850000</v>
       </c>
       <c r="M18" t="n">
-        <v>8.16</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1625,40 +1625,40 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F19" t="n">
-        <v>80750000</v>
+        <v>52900000</v>
       </c>
       <c r="G19" t="n">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="H19" t="n">
-        <v>486515000</v>
+        <v>498800000</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>189240000</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1672,40 +1672,40 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>55500000</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="H20" t="n">
-        <v>400400000</v>
+        <v>373965000</v>
       </c>
       <c r="I20" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="J20" t="n">
-        <v>17400000</v>
+        <v>93800000</v>
       </c>
       <c r="K20" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="L20" t="n">
-        <v>63370000</v>
+        <v>82770000</v>
       </c>
       <c r="M20" t="n">
-        <v>15.83</v>
+        <v>22.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,40 +1719,40 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>61800000</v>
+        <v>9300000</v>
       </c>
       <c r="G21" t="n">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="H21" t="n">
-        <v>502442000</v>
+        <v>482122000</v>
       </c>
       <c r="I21" t="n">
-        <v>64</v>
+        <v>221</v>
       </c>
       <c r="J21" t="n">
-        <v>50200000</v>
+        <v>215720000</v>
       </c>
       <c r="K21" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L21" t="n">
-        <v>87972000</v>
+        <v>100142000</v>
       </c>
       <c r="M21" t="n">
-        <v>17.51</v>
+        <v>20.77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,40 +1766,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>94200000</v>
+        <v>9000000</v>
       </c>
       <c r="G22" t="n">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="H22" t="n">
-        <v>764380000</v>
+        <v>718040000</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>199</v>
       </c>
       <c r="J22" t="n">
-        <v>22300000</v>
+        <v>288175000</v>
       </c>
       <c r="K22" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="L22" t="n">
-        <v>48975000</v>
+        <v>65425000</v>
       </c>
       <c r="M22" t="n">
-        <v>6.41</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1813,25 +1813,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>47500000</v>
+        <v>4200000</v>
       </c>
       <c r="G23" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H23" t="n">
-        <v>91060000</v>
+        <v>93660000</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>250000</v>
+        <v>28650000</v>
       </c>
       <c r="K23" t="n">
         <v>50</v>
@@ -1840,13 +1840,13 @@
         <v>27860000</v>
       </c>
       <c r="M23" t="n">
-        <v>30.6</v>
+        <v>29.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,34 +1860,34 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>84100000</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="H24" t="n">
-        <v>393175000</v>
+        <v>365325000</v>
       </c>
       <c r="I24" t="n">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="J24" t="n">
-        <v>25650000</v>
+        <v>73650000</v>
       </c>
       <c r="K24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L24" t="n">
-        <v>8375000</v>
+        <v>24700000</v>
       </c>
       <c r="M24" t="n">
-        <v>2.13</v>
+        <v>6.76</v>
       </c>
     </row>
   </sheetData>
@@ -2192,10 +2192,10 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>435900000</v>
+        <v>157100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>359094000</v>
+        <v>511328000</v>
       </c>
     </row>
     <row r="3">
@@ -2243,10 +2243,10 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>423850000</v>
+        <v>75400000</v>
       </c>
       <c r="Q3" t="n">
-        <v>230472000</v>
+        <v>334632000</v>
       </c>
     </row>
     <row r="4">
@@ -2294,10 +2294,10 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>424900000</v>
+        <v>60900000</v>
       </c>
       <c r="Q4" t="n">
-        <v>499089000</v>
+        <v>633489000</v>
       </c>
     </row>
     <row r="5">
@@ -2345,10 +2345,10 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>397290000</v>
+        <v>63420000</v>
       </c>
       <c r="Q5" t="n">
-        <v>348535001</v>
+        <v>438938001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>633489000</v>
+        <v>548069000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>511328000</v>
+        <v>414708000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>438938001</v>
+        <v>374260001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>334632000</v>
+        <v>262927000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,64 +526,64 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>70200000</v>
+        <v>129000000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>43100000</v>
+        <v>120400000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>41600000</v>
+        <v>112650000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>30900000</v>
+        <v>112100000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,22 +644,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>157100000</v>
+        <v>197050000</v>
       </c>
       <c r="D2" t="n">
-        <v>2397</v>
+        <v>2364</v>
       </c>
       <c r="E2" t="n">
-        <v>3365966000</v>
+        <v>3265043000</v>
       </c>
       <c r="F2" t="n">
-        <v>457586000</v>
+        <v>422856000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,22 +668,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>75400000</v>
+        <v>178750000</v>
       </c>
       <c r="D3" t="n">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="E3" t="n">
-        <v>2531912000</v>
+        <v>2510307000</v>
       </c>
       <c r="F3" t="n">
-        <v>302397000</v>
+        <v>261227000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>63420000</v>
+        <v>145620000</v>
       </c>
       <c r="D4" t="n">
-        <v>2231</v>
+        <v>2216</v>
       </c>
       <c r="E4" t="n">
-        <v>2749689000</v>
+        <v>2718351000</v>
       </c>
       <c r="F4" t="n">
-        <v>371655000</v>
+        <v>358080000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>60900000</v>
+        <v>122900000</v>
       </c>
       <c r="D5" t="n">
-        <v>2530</v>
+        <v>2512</v>
       </c>
       <c r="E5" t="n">
-        <v>3087146000</v>
+        <v>3012558000</v>
       </c>
       <c r="F5" t="n">
-        <v>561101000</v>
+        <v>515841000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>4500000</v>
+        <v>9500000</v>
       </c>
       <c r="G2" t="n">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="H2" t="n">
-        <v>568620000</v>
+        <v>548045000</v>
       </c>
       <c r="I2" t="n">
-        <v>132</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>161875000</v>
+        <v>1250000</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +873,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>6000000</v>
+        <v>16200000</v>
       </c>
       <c r="G3" t="n">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="H3" t="n">
-        <v>550804000</v>
+        <v>542366000</v>
       </c>
       <c r="I3" t="n">
-        <v>148</v>
+        <v>57</v>
       </c>
       <c r="J3" t="n">
-        <v>159635000</v>
+        <v>47395000</v>
       </c>
       <c r="K3" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="L3" t="n">
-        <v>183971000</v>
+        <v>179531000</v>
       </c>
       <c r="M3" t="n">
-        <v>33.4</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,31 +929,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H4" t="n">
-        <v>163750000</v>
+        <v>159425000</v>
       </c>
       <c r="I4" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>18210000</v>
+        <v>8760000</v>
       </c>
       <c r="K4" t="n">
         <v>106</v>
       </c>
       <c r="L4" t="n">
-        <v>128040000</v>
+        <v>126665000</v>
       </c>
       <c r="M4" t="n">
-        <v>78.19</v>
+        <v>79.45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,40 +967,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
-        <v>34200000</v>
+        <v>58800000</v>
       </c>
       <c r="G5" t="n">
         <v>449</v>
       </c>
       <c r="H5" t="n">
-        <v>809955000</v>
+        <v>795195000</v>
       </c>
       <c r="I5" t="n">
-        <v>186</v>
+        <v>45</v>
       </c>
       <c r="J5" t="n">
-        <v>324115000</v>
+        <v>85175000</v>
       </c>
       <c r="K5" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L5" t="n">
-        <v>43545000</v>
+        <v>29395000</v>
       </c>
       <c r="M5" t="n">
-        <v>5.38</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>3000000</v>
+        <v>6600000</v>
       </c>
       <c r="G6" t="n">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="H6" t="n">
-        <v>448927000</v>
+        <v>438672000</v>
       </c>
       <c r="I6" t="n">
-        <v>213</v>
+        <v>135</v>
       </c>
       <c r="J6" t="n">
-        <v>165502000</v>
+        <v>93347000</v>
       </c>
       <c r="K6" t="n">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="L6" t="n">
-        <v>120985000</v>
+        <v>116625000</v>
       </c>
       <c r="M6" t="n">
-        <v>26.95</v>
+        <v>26.59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,40 +1061,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>13200000</v>
+        <v>31800000</v>
       </c>
       <c r="G7" t="n">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="H7" t="n">
-        <v>545090000</v>
+        <v>528855000</v>
       </c>
       <c r="I7" t="n">
-        <v>344</v>
+        <v>168</v>
       </c>
       <c r="J7" t="n">
-        <v>320310000</v>
+        <v>129185000</v>
       </c>
       <c r="K7" t="n">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="L7" t="n">
-        <v>84560000</v>
+        <v>63625000</v>
       </c>
       <c r="M7" t="n">
-        <v>15.51</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,40 +1108,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>3600000</v>
+        <v>14400000</v>
       </c>
       <c r="G8" t="n">
-        <v>383</v>
+        <v>344</v>
       </c>
       <c r="H8" t="n">
-        <v>377824000</v>
+        <v>343966000</v>
       </c>
       <c r="I8" t="n">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="J8" t="n">
-        <v>110799000</v>
+        <v>40015000</v>
       </c>
       <c r="K8" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="L8" t="n">
-        <v>118640000</v>
+        <v>86630000</v>
       </c>
       <c r="M8" t="n">
-        <v>31.4</v>
+        <v>25.19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1164,31 +1164,31 @@
         <v>10320000</v>
       </c>
       <c r="G9" t="n">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="H9" t="n">
-        <v>233915000</v>
+        <v>260950000</v>
       </c>
       <c r="I9" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="J9" t="n">
-        <v>62370000</v>
+        <v>17640000</v>
       </c>
       <c r="K9" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="L9" t="n">
-        <v>40590000</v>
+        <v>71975000</v>
       </c>
       <c r="M9" t="n">
-        <v>17.35</v>
+        <v>27.58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,40 +1202,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>12600000</v>
+        <v>24600000</v>
       </c>
       <c r="G10" t="n">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="H10" t="n">
-        <v>511595000</v>
+        <v>493750000</v>
       </c>
       <c r="I10" t="n">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
-        <v>194760000</v>
+        <v>24540000</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>16850000</v>
+        <v>8500000</v>
       </c>
       <c r="M10" t="n">
-        <v>3.29</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,40 +1249,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F11" t="n">
-        <v>36900000</v>
+        <v>71100000</v>
       </c>
       <c r="G11" t="n">
         <v>479</v>
       </c>
       <c r="H11" t="n">
-        <v>841164000</v>
+        <v>841479000</v>
       </c>
       <c r="I11" t="n">
-        <v>160</v>
+        <v>26</v>
       </c>
       <c r="J11" t="n">
-        <v>239275000</v>
+        <v>30600000</v>
       </c>
       <c r="K11" t="n">
         <v>17</v>
       </c>
       <c r="L11" t="n">
-        <v>26075000</v>
+        <v>25725000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,25 +1296,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>17400000</v>
       </c>
       <c r="G12" t="n">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="H12" t="n">
-        <v>400071000</v>
+        <v>400351000</v>
       </c>
       <c r="I12" t="n">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>90160000</v>
+        <v>6500000</v>
       </c>
       <c r="K12" t="n">
         <v>56</v>
@@ -1323,13 +1323,13 @@
         <v>56005000</v>
       </c>
       <c r="M12" t="n">
-        <v>14</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,40 +1343,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>7800000</v>
       </c>
       <c r="G13" t="n">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="H13" t="n">
-        <v>385120000</v>
+        <v>377855000</v>
       </c>
       <c r="I13" t="n">
-        <v>181</v>
+        <v>76</v>
       </c>
       <c r="J13" t="n">
-        <v>128895000</v>
+        <v>50610000</v>
       </c>
       <c r="K13" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="L13" t="n">
-        <v>113495000</v>
+        <v>109245000</v>
       </c>
       <c r="M13" t="n">
-        <v>29.47</v>
+        <v>28.91</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1390,40 +1390,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F14" t="n">
-        <v>64200000</v>
+        <v>69450000</v>
       </c>
       <c r="G14" t="n">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="H14" t="n">
-        <v>737051000</v>
+        <v>706549000</v>
       </c>
       <c r="I14" t="n">
-        <v>189</v>
+        <v>59</v>
       </c>
       <c r="J14" t="n">
-        <v>226966000</v>
+        <v>54236000</v>
       </c>
       <c r="K14" t="n">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="L14" t="n">
-        <v>77356000</v>
+        <v>72006000</v>
       </c>
       <c r="M14" t="n">
-        <v>10.5</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1437,40 +1437,40 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>31200000</v>
+        <v>40800000</v>
       </c>
       <c r="G15" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H15" t="n">
-        <v>610810000</v>
+        <v>602170000</v>
       </c>
       <c r="I15" t="n">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
-        <v>141255000</v>
+        <v>9500000</v>
       </c>
       <c r="K15" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L15" t="n">
-        <v>97975000</v>
+        <v>93475000</v>
       </c>
       <c r="M15" t="n">
-        <v>16.04</v>
+        <v>15.52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1484,40 +1484,40 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>21100000</v>
+        <v>33000000</v>
       </c>
       <c r="G16" t="n">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="H16" t="n">
-        <v>376240000</v>
+        <v>370135000</v>
       </c>
       <c r="I16" t="n">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>92300000</v>
+        <v>21375000</v>
       </c>
       <c r="K16" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="L16" t="n">
-        <v>133980000</v>
+        <v>121775000</v>
       </c>
       <c r="M16" t="n">
-        <v>35.61</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,40 +1531,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>7200000</v>
       </c>
       <c r="G17" t="n">
-        <v>592</v>
+        <v>577</v>
       </c>
       <c r="H17" t="n">
-        <v>940112000</v>
+        <v>913527000</v>
       </c>
       <c r="I17" t="n">
-        <v>275</v>
+        <v>133</v>
       </c>
       <c r="J17" t="n">
-        <v>417296000</v>
+        <v>206646000</v>
       </c>
       <c r="K17" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="L17" t="n">
-        <v>84425000</v>
+        <v>78950000</v>
       </c>
       <c r="M17" t="n">
-        <v>8.98</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,40 +1578,40 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F18" t="n">
-        <v>40600000</v>
+        <v>46600000</v>
       </c>
       <c r="G18" t="n">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="H18" t="n">
-        <v>701753000</v>
+        <v>672662000</v>
       </c>
       <c r="I18" t="n">
-        <v>214</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>248653000</v>
+        <v>29475000</v>
       </c>
       <c r="K18" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="L18" t="n">
-        <v>63850000</v>
+        <v>56650000</v>
       </c>
       <c r="M18" t="n">
-        <v>9.1</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1625,40 +1625,40 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F19" t="n">
-        <v>52900000</v>
+        <v>71500000</v>
       </c>
       <c r="G19" t="n">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="H19" t="n">
-        <v>498800000</v>
+        <v>482265000</v>
       </c>
       <c r="I19" t="n">
-        <v>196</v>
+        <v>9</v>
       </c>
       <c r="J19" t="n">
-        <v>189240000</v>
+        <v>2800000</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1672,40 +1672,40 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>22250000</v>
       </c>
       <c r="G20" t="n">
         <v>315</v>
       </c>
       <c r="H20" t="n">
-        <v>373965000</v>
+        <v>380520000</v>
       </c>
       <c r="I20" t="n">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="J20" t="n">
-        <v>93800000</v>
+        <v>32050000</v>
       </c>
       <c r="K20" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="L20" t="n">
-        <v>82770000</v>
+        <v>63820000</v>
       </c>
       <c r="M20" t="n">
-        <v>22.13</v>
+        <v>16.77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,40 +1719,40 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F21" t="n">
-        <v>9300000</v>
+        <v>39100000</v>
       </c>
       <c r="G21" t="n">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="H21" t="n">
-        <v>482122000</v>
+        <v>491772000</v>
       </c>
       <c r="I21" t="n">
-        <v>221</v>
+        <v>135</v>
       </c>
       <c r="J21" t="n">
-        <v>215720000</v>
+        <v>119950000</v>
       </c>
       <c r="K21" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="L21" t="n">
-        <v>100142000</v>
+        <v>86822000</v>
       </c>
       <c r="M21" t="n">
-        <v>20.77</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,40 +1766,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F22" t="n">
-        <v>9000000</v>
+        <v>41700000</v>
       </c>
       <c r="G22" t="n">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="H22" t="n">
-        <v>718040000</v>
+        <v>710940000</v>
       </c>
       <c r="I22" t="n">
-        <v>199</v>
+        <v>48</v>
       </c>
       <c r="J22" t="n">
-        <v>288175000</v>
+        <v>55625000</v>
       </c>
       <c r="K22" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L22" t="n">
-        <v>65425000</v>
+        <v>63025000</v>
       </c>
       <c r="M22" t="n">
-        <v>9.109999999999999</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1822,31 +1822,31 @@
         <v>4200000</v>
       </c>
       <c r="G23" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H23" t="n">
-        <v>93660000</v>
+        <v>90010000</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>28650000</v>
+        <v>4050000</v>
       </c>
       <c r="K23" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="L23" t="n">
-        <v>27860000</v>
+        <v>26710000</v>
       </c>
       <c r="M23" t="n">
-        <v>29.75</v>
+        <v>29.67</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1872,22 +1872,22 @@
         <v>274</v>
       </c>
       <c r="H24" t="n">
-        <v>365325000</v>
+        <v>354800000</v>
       </c>
       <c r="I24" t="n">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>73650000</v>
+        <v>15450000</v>
       </c>
       <c r="K24" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L24" t="n">
-        <v>24700000</v>
+        <v>20850000</v>
       </c>
       <c r="M24" t="n">
-        <v>6.76</v>
+        <v>5.88</v>
       </c>
     </row>
   </sheetData>
@@ -2192,10 +2192,10 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>157100000</v>
+        <v>197050000</v>
       </c>
       <c r="Q2" t="n">
-        <v>511328000</v>
+        <v>414708000</v>
       </c>
     </row>
     <row r="3">
@@ -2243,10 +2243,10 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>75400000</v>
+        <v>178750000</v>
       </c>
       <c r="Q3" t="n">
-        <v>334632000</v>
+        <v>262927000</v>
       </c>
     </row>
     <row r="4">
@@ -2294,10 +2294,10 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>60900000</v>
+        <v>122900000</v>
       </c>
       <c r="Q4" t="n">
-        <v>633489000</v>
+        <v>548069000</v>
       </c>
     </row>
     <row r="5">
@@ -2345,10 +2345,10 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>63420000</v>
+        <v>145620000</v>
       </c>
       <c r="Q5" t="n">
-        <v>438938001</v>
+        <v>374260001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>548069000</v>
+        <v>547709000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>414708000</v>
+        <v>413808000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>374260001</v>
+        <v>370735001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>262927000</v>
+        <v>262477000</v>
       </c>
     </row>
   </sheetData>
@@ -522,14 +522,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>129000000</v>
+        <v>112100000</v>
       </c>
     </row>
     <row r="3">
@@ -540,14 +540,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>120400000</v>
+        <v>103500000</v>
       </c>
     </row>
     <row r="4">
@@ -558,14 +558,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>112650000</v>
+        <v>90400000</v>
       </c>
     </row>
     <row r="5">
@@ -576,14 +576,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>112100000</v>
+        <v>69600000</v>
       </c>
     </row>
   </sheetData>
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>197050000</v>
+        <v>242600000</v>
       </c>
       <c r="D2" t="n">
-        <v>2364</v>
+        <v>2371</v>
       </c>
       <c r="E2" t="n">
-        <v>3265043000</v>
+        <v>3305893000</v>
       </c>
       <c r="F2" t="n">
         <v>422856000</v>
@@ -674,7 +674,7 @@
         <v>2115</v>
       </c>
       <c r="E3" t="n">
-        <v>2510307000</v>
+        <v>2509857000</v>
       </c>
       <c r="F3" t="n">
         <v>261227000</v>
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>145620000</v>
+        <v>164520000</v>
       </c>
       <c r="D4" t="n">
-        <v>2216</v>
+        <v>2223</v>
       </c>
       <c r="E4" t="n">
-        <v>2718351000</v>
+        <v>2734101000</v>
       </c>
       <c r="F4" t="n">
         <v>358080000</v>
@@ -716,13 +716,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>122900000</v>
+        <v>152900000</v>
       </c>
       <c r="D5" t="n">
-        <v>2512</v>
+        <v>2514</v>
       </c>
       <c r="E5" t="n">
-        <v>3012558000</v>
+        <v>3038798000</v>
       </c>
       <c r="F5" t="n">
         <v>515841000</v>
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>9500000</v>
+        <v>23900000</v>
       </c>
       <c r="G2" t="n">
         <v>358</v>
       </c>
       <c r="H2" t="n">
-        <v>548045000</v>
+        <v>560545000</v>
       </c>
       <c r="I2" t="n">
         <v>6</v>
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>16200000</v>
+        <v>22200000</v>
       </c>
       <c r="G3" t="n">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="H3" t="n">
-        <v>542366000</v>
+        <v>548366000</v>
       </c>
       <c r="I3" t="n">
         <v>57</v>
@@ -900,7 +900,7 @@
         <v>179531000</v>
       </c>
       <c r="M3" t="n">
-        <v>33.1</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="4">
@@ -967,19 +967,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>58800000</v>
+        <v>68400000</v>
       </c>
       <c r="G5" t="n">
         <v>449</v>
       </c>
       <c r="H5" t="n">
-        <v>795195000</v>
+        <v>803295000</v>
       </c>
       <c r="I5" t="n">
         <v>45</v>
@@ -994,7 +994,7 @@
         <v>29395000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="6">
@@ -1026,13 +1026,13 @@
         <v>522</v>
       </c>
       <c r="H6" t="n">
-        <v>438672000</v>
+        <v>438312000</v>
       </c>
       <c r="I6" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J6" t="n">
-        <v>93347000</v>
+        <v>90467000</v>
       </c>
       <c r="K6" t="n">
         <v>154</v>
@@ -1041,7 +1041,7 @@
         <v>116625000</v>
       </c>
       <c r="M6" t="n">
-        <v>26.59</v>
+        <v>26.61</v>
       </c>
     </row>
     <row r="7">
@@ -1120,13 +1120,13 @@
         <v>344</v>
       </c>
       <c r="H8" t="n">
-        <v>343966000</v>
+        <v>342616000</v>
       </c>
       <c r="I8" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="J8" t="n">
-        <v>40015000</v>
+        <v>31015000</v>
       </c>
       <c r="K8" t="n">
         <v>116</v>
@@ -1135,7 +1135,7 @@
         <v>86630000</v>
       </c>
       <c r="M8" t="n">
-        <v>25.19</v>
+        <v>25.28</v>
       </c>
     </row>
     <row r="9">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F9" t="n">
-        <v>10320000</v>
+        <v>22620000</v>
       </c>
       <c r="G9" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="H9" t="n">
-        <v>260950000</v>
+        <v>273250000</v>
       </c>
       <c r="I9" t="n">
         <v>12</v>
@@ -1182,7 +1182,7 @@
         <v>71975000</v>
       </c>
       <c r="M9" t="n">
-        <v>27.58</v>
+        <v>26.34</v>
       </c>
     </row>
     <row r="10">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>24600000</v>
+        <v>31200000</v>
       </c>
       <c r="G10" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H10" t="n">
-        <v>493750000</v>
+        <v>500350000</v>
       </c>
       <c r="I10" t="n">
         <v>19</v>
@@ -1229,7 +1229,7 @@
         <v>8500000</v>
       </c>
       <c r="M10" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11">
@@ -1261,13 +1261,13 @@
         <v>479</v>
       </c>
       <c r="H11" t="n">
-        <v>841479000</v>
+        <v>839679000</v>
       </c>
       <c r="I11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J11" t="n">
-        <v>30600000</v>
+        <v>23400000</v>
       </c>
       <c r="K11" t="n">
         <v>17</v>
@@ -1390,25 +1390,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F14" t="n">
-        <v>69450000</v>
+        <v>89100000</v>
       </c>
       <c r="G14" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="H14" t="n">
-        <v>706549000</v>
+        <v>723599000</v>
       </c>
       <c r="I14" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="J14" t="n">
-        <v>54236000</v>
+        <v>51236000</v>
       </c>
       <c r="K14" t="n">
         <v>93</v>
@@ -1417,7 +1417,7 @@
         <v>72006000</v>
       </c>
       <c r="M14" t="n">
-        <v>10.19</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1484,19 +1484,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F16" t="n">
-        <v>33000000</v>
+        <v>39000000</v>
       </c>
       <c r="G16" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H16" t="n">
-        <v>370135000</v>
+        <v>376135000</v>
       </c>
       <c r="I16" t="n">
         <v>26</v>
@@ -1511,7 +1511,7 @@
         <v>121775000</v>
       </c>
       <c r="M16" t="n">
-        <v>32.9</v>
+        <v>32.38</v>
       </c>
     </row>
     <row r="17">
@@ -1531,19 +1531,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>7200000</v>
+        <v>18700000</v>
       </c>
       <c r="G17" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="H17" t="n">
-        <v>913527000</v>
+        <v>923827000</v>
       </c>
       <c r="I17" t="n">
         <v>133</v>
@@ -1558,7 +1558,7 @@
         <v>78950000</v>
       </c>
       <c r="M17" t="n">
-        <v>8.640000000000001</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1578,25 +1578,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F18" t="n">
-        <v>46600000</v>
+        <v>55000000</v>
       </c>
       <c r="G18" t="n">
         <v>585</v>
       </c>
       <c r="H18" t="n">
-        <v>672662000</v>
+        <v>680162000</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>29475000</v>
+        <v>28575000</v>
       </c>
       <c r="K18" t="n">
         <v>61</v>
@@ -1605,7 +1605,7 @@
         <v>56650000</v>
       </c>
       <c r="M18" t="n">
-        <v>8.42</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="19">
@@ -1778,13 +1778,13 @@
         <v>488</v>
       </c>
       <c r="H22" t="n">
-        <v>710940000</v>
+        <v>710490000</v>
       </c>
       <c r="I22" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J22" t="n">
-        <v>55625000</v>
+        <v>52925000</v>
       </c>
       <c r="K22" t="n">
         <v>41</v>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>177409000</v>
+        <v>88919000</v>
       </c>
     </row>
     <row r="3">
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>156267750</v>
+        <v>75623000</v>
       </c>
     </row>
     <row r="4">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>359193040</v>
+        <v>229435310</v>
       </c>
     </row>
     <row r="5">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>122803750</v>
+        <v>58814500</v>
       </c>
     </row>
     <row r="6">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>415624500</v>
+        <v>418449500</v>
       </c>
     </row>
     <row r="7">
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>263521640</v>
+        <v>134972330</v>
       </c>
     </row>
   </sheetData>
@@ -2057,7 +2057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2103,45 +2103,10 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>صرف_2026-04</t>
+          <t>صرف_None</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
-        <is>
-          <t>متأخر_2026-04</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>صرف_2026-05</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>متأخر_2026-05</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>صرف_2026-06</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>متأخر_2026-06</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Unnamed: 14</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>صرف_None</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
         <is>
           <t>متأخر_None</t>
         </is>
@@ -2173,29 +2138,10 @@
         <v>324966000</v>
       </c>
       <c r="I2" t="n">
-        <v>358840000</v>
+        <v>242600000</v>
       </c>
       <c r="J2" t="n">
-        <v>327656000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>488300000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>328441000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>467500000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>336401000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>197050000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>414708000</v>
+        <v>413808000</v>
       </c>
     </row>
     <row r="3">
@@ -2224,29 +2170,10 @@
         <v>194867000</v>
       </c>
       <c r="I3" t="n">
-        <v>408650000</v>
+        <v>178750000</v>
       </c>
       <c r="J3" t="n">
-        <v>192417000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>369250000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>201892000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>357300000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>211112000</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>178750000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>262927000</v>
+        <v>262477000</v>
       </c>
     </row>
     <row r="4">
@@ -2275,29 +2202,10 @@
         <v>459416000</v>
       </c>
       <c r="I4" t="n">
-        <v>395150000</v>
+        <v>152900000</v>
       </c>
       <c r="J4" t="n">
-        <v>457931000</v>
-      </c>
-      <c r="K4" t="n">
-        <v>392690000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>461506000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>457200000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>465566000</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>122900000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>548069000</v>
+        <v>547709000</v>
       </c>
     </row>
     <row r="5">
@@ -2326,29 +2234,10 @@
         <v>365124001</v>
       </c>
       <c r="I5" t="n">
-        <v>316800000</v>
+        <v>164520000</v>
       </c>
       <c r="J5" t="n">
-        <v>356554001</v>
-      </c>
-      <c r="K5" t="n">
-        <v>305360000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>358139001</v>
-      </c>
-      <c r="M5" t="n">
-        <v>462000000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>353144001</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>145620000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>374260001</v>
+        <v>370735001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,70 +644,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>242600000</v>
+        <v>409100000</v>
       </c>
       <c r="D2" t="n">
-        <v>2371</v>
+        <v>2402</v>
       </c>
       <c r="E2" t="n">
-        <v>3305893000</v>
+        <v>3436214000</v>
       </c>
       <c r="F2" t="n">
-        <v>422856000</v>
+        <v>404131000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>178750000</v>
+        <v>320720000</v>
       </c>
       <c r="D3" t="n">
-        <v>2115</v>
+        <v>2275</v>
       </c>
       <c r="E3" t="n">
-        <v>2509857000</v>
+        <v>2868511000</v>
       </c>
       <c r="F3" t="n">
-        <v>261227000</v>
+        <v>357680000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>164520000</v>
+        <v>318200000</v>
       </c>
       <c r="D4" t="n">
-        <v>2223</v>
+        <v>2172</v>
       </c>
       <c r="E4" t="n">
-        <v>2734101000</v>
+        <v>2625852000</v>
       </c>
       <c r="F4" t="n">
-        <v>358080000</v>
+        <v>257777000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>152900000</v>
+        <v>302160000</v>
       </c>
       <c r="D5" t="n">
-        <v>2514</v>
+        <v>2576</v>
       </c>
       <c r="E5" t="n">
-        <v>3038798000</v>
+        <v>3130438000</v>
       </c>
       <c r="F5" t="n">
-        <v>515841000</v>
+        <v>500346000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F2" t="n">
-        <v>23900000</v>
+        <v>41900000</v>
       </c>
       <c r="G2" t="n">
         <v>358</v>
       </c>
       <c r="H2" t="n">
-        <v>560545000</v>
+        <v>562345000</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1250000</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +873,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F3" t="n">
-        <v>22200000</v>
+        <v>37200000</v>
       </c>
       <c r="G3" t="n">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="H3" t="n">
-        <v>548366000</v>
+        <v>560916000</v>
       </c>
       <c r="I3" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="J3" t="n">
-        <v>47395000</v>
+        <v>35845000</v>
       </c>
       <c r="K3" t="n">
         <v>194</v>
       </c>
       <c r="L3" t="n">
-        <v>179531000</v>
+        <v>179331000</v>
       </c>
       <c r="M3" t="n">
-        <v>32.74</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -932,28 +932,28 @@
         <v>168</v>
       </c>
       <c r="H4" t="n">
-        <v>159425000</v>
+        <v>158200000</v>
       </c>
       <c r="I4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>8760000</v>
+        <v>5460000</v>
       </c>
       <c r="K4" t="n">
         <v>106</v>
       </c>
       <c r="L4" t="n">
-        <v>126665000</v>
+        <v>126415000</v>
       </c>
       <c r="M4" t="n">
-        <v>79.45</v>
+        <v>79.91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -967,25 +967,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="F5" t="n">
-        <v>68400000</v>
+        <v>122960000</v>
       </c>
       <c r="G5" t="n">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="H5" t="n">
-        <v>803295000</v>
+        <v>833955000</v>
       </c>
       <c r="I5" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>85175000</v>
+        <v>19325000</v>
       </c>
       <c r="K5" t="n">
         <v>21</v>
@@ -994,13 +994,13 @@
         <v>29395000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.66</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>6600000</v>
+        <v>53000000</v>
       </c>
       <c r="G6" t="n">
-        <v>522</v>
+        <v>556</v>
       </c>
       <c r="H6" t="n">
-        <v>438312000</v>
+        <v>479762000</v>
       </c>
       <c r="I6" t="n">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="J6" t="n">
-        <v>90467000</v>
+        <v>67487000</v>
       </c>
       <c r="K6" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="L6" t="n">
-        <v>116625000</v>
+        <v>115275000</v>
       </c>
       <c r="M6" t="n">
-        <v>26.61</v>
+        <v>24.03</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,40 +1061,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F7" t="n">
-        <v>31800000</v>
+        <v>47100000</v>
       </c>
       <c r="G7" t="n">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="H7" t="n">
-        <v>528855000</v>
+        <v>535260000</v>
       </c>
       <c r="I7" t="n">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="J7" t="n">
-        <v>129185000</v>
+        <v>92675000</v>
       </c>
       <c r="K7" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="L7" t="n">
-        <v>63625000</v>
+        <v>49930000</v>
       </c>
       <c r="M7" t="n">
-        <v>12.03</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,25 +1108,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F8" t="n">
-        <v>14400000</v>
+        <v>41700000</v>
       </c>
       <c r="G8" t="n">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="H8" t="n">
-        <v>342616000</v>
+        <v>366061000</v>
       </c>
       <c r="I8" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="J8" t="n">
-        <v>31015000</v>
+        <v>22240000</v>
       </c>
       <c r="K8" t="n">
         <v>116</v>
@@ -1135,13 +1135,13 @@
         <v>86630000</v>
       </c>
       <c r="M8" t="n">
-        <v>25.28</v>
+        <v>23.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1155,25 +1155,25 @@
         </is>
       </c>
       <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" t="n">
+        <v>37620000</v>
+      </c>
+      <c r="G9" t="n">
+        <v>231</v>
+      </c>
+      <c r="H9" t="n">
+        <v>287100000</v>
+      </c>
+      <c r="I9" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="n">
-        <v>12</v>
-      </c>
-      <c r="F9" t="n">
-        <v>22620000</v>
-      </c>
-      <c r="G9" t="n">
-        <v>223</v>
-      </c>
-      <c r="H9" t="n">
-        <v>273250000</v>
-      </c>
-      <c r="I9" t="n">
-        <v>12</v>
-      </c>
       <c r="J9" t="n">
-        <v>17640000</v>
+        <v>7240000</v>
       </c>
       <c r="K9" t="n">
         <v>92</v>
@@ -1182,13 +1182,13 @@
         <v>71975000</v>
       </c>
       <c r="M9" t="n">
-        <v>26.34</v>
+        <v>25.07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>31200000</v>
+        <v>70400000</v>
       </c>
       <c r="G10" t="n">
         <v>381</v>
       </c>
       <c r="H10" t="n">
-        <v>500350000</v>
+        <v>530190000</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>24540000</v>
+        <v>9750000</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
@@ -1229,13 +1229,13 @@
         <v>8500000</v>
       </c>
       <c r="M10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1249,40 +1249,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F11" t="n">
-        <v>71100000</v>
+        <v>90900000</v>
       </c>
       <c r="G11" t="n">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="H11" t="n">
-        <v>839679000</v>
+        <v>855454000</v>
       </c>
       <c r="I11" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J11" t="n">
-        <v>23400000</v>
+        <v>19350000</v>
       </c>
       <c r="K11" t="n">
         <v>17</v>
       </c>
       <c r="L11" t="n">
-        <v>25725000</v>
+        <v>25575000</v>
       </c>
       <c r="M11" t="n">
-        <v>3.06</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F12" t="n">
-        <v>17400000</v>
+        <v>54300000</v>
       </c>
       <c r="G12" t="n">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="H12" t="n">
-        <v>400351000</v>
+        <v>436551000</v>
       </c>
       <c r="I12" t="n">
         <v>3</v>
@@ -1320,16 +1320,16 @@
         <v>56</v>
       </c>
       <c r="L12" t="n">
-        <v>56005000</v>
+        <v>55755000</v>
       </c>
       <c r="M12" t="n">
-        <v>13.99</v>
+        <v>12.77</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,25 +1343,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F13" t="n">
-        <v>7800000</v>
+        <v>25800000</v>
       </c>
       <c r="G13" t="n">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="H13" t="n">
-        <v>377855000</v>
+        <v>393155000</v>
       </c>
       <c r="I13" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="J13" t="n">
-        <v>50610000</v>
+        <v>35220000</v>
       </c>
       <c r="K13" t="n">
         <v>138</v>
@@ -1370,13 +1370,13 @@
         <v>109245000</v>
       </c>
       <c r="M13" t="n">
-        <v>28.91</v>
+        <v>27.79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1399,31 +1399,31 @@
         <v>89100000</v>
       </c>
       <c r="G14" t="n">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="H14" t="n">
-        <v>723599000</v>
+        <v>717960000</v>
       </c>
       <c r="I14" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="J14" t="n">
-        <v>51236000</v>
+        <v>31420000</v>
       </c>
       <c r="K14" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="L14" t="n">
-        <v>72006000</v>
+        <v>67481000</v>
       </c>
       <c r="M14" t="n">
-        <v>9.949999999999999</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1437,40 +1437,40 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F15" t="n">
-        <v>40800000</v>
+        <v>95400000</v>
       </c>
       <c r="G15" t="n">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="H15" t="n">
-        <v>602170000</v>
+        <v>649220000</v>
       </c>
       <c r="I15" t="n">
         <v>7</v>
       </c>
       <c r="J15" t="n">
-        <v>9500000</v>
+        <v>13500000</v>
       </c>
       <c r="K15" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L15" t="n">
-        <v>93475000</v>
+        <v>79275000</v>
       </c>
       <c r="M15" t="n">
-        <v>15.52</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1484,25 +1484,25 @@
         </is>
       </c>
       <c r="D16" t="n">
+        <v>13</v>
+      </c>
+      <c r="E16" t="n">
+        <v>37</v>
+      </c>
+      <c r="F16" t="n">
+        <v>79800000</v>
+      </c>
+      <c r="G16" t="n">
+        <v>329</v>
+      </c>
+      <c r="H16" t="n">
+        <v>410345000</v>
+      </c>
+      <c r="I16" t="n">
         <v>6</v>
       </c>
-      <c r="E16" t="n">
-        <v>17</v>
-      </c>
-      <c r="F16" t="n">
-        <v>39000000</v>
-      </c>
-      <c r="G16" t="n">
-        <v>320</v>
-      </c>
-      <c r="H16" t="n">
-        <v>376135000</v>
-      </c>
-      <c r="I16" t="n">
-        <v>26</v>
-      </c>
       <c r="J16" t="n">
-        <v>21375000</v>
+        <v>1785000</v>
       </c>
       <c r="K16" t="n">
         <v>98</v>
@@ -1511,13 +1511,13 @@
         <v>121775000</v>
       </c>
       <c r="M16" t="n">
-        <v>32.38</v>
+        <v>29.68</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,25 +1531,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="F17" t="n">
-        <v>18700000</v>
+        <v>79000000</v>
       </c>
       <c r="G17" t="n">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="H17" t="n">
-        <v>923827000</v>
+        <v>975002000</v>
       </c>
       <c r="I17" t="n">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="J17" t="n">
-        <v>206646000</v>
+        <v>165721000</v>
       </c>
       <c r="K17" t="n">
         <v>75</v>
@@ -1558,13 +1558,13 @@
         <v>78950000</v>
       </c>
       <c r="M17" t="n">
-        <v>8.550000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,25 +1578,25 @@
         </is>
       </c>
       <c r="D18" t="n">
+        <v>13</v>
+      </c>
+      <c r="E18" t="n">
+        <v>39</v>
+      </c>
+      <c r="F18" t="n">
+        <v>65800000</v>
+      </c>
+      <c r="G18" t="n">
+        <v>578</v>
+      </c>
+      <c r="H18" t="n">
+        <v>683687000</v>
+      </c>
+      <c r="I18" t="n">
         <v>11</v>
       </c>
-      <c r="E18" t="n">
-        <v>33</v>
-      </c>
-      <c r="F18" t="n">
-        <v>55000000</v>
-      </c>
-      <c r="G18" t="n">
-        <v>585</v>
-      </c>
-      <c r="H18" t="n">
-        <v>680162000</v>
-      </c>
-      <c r="I18" t="n">
-        <v>23</v>
-      </c>
       <c r="J18" t="n">
-        <v>28575000</v>
+        <v>23500000</v>
       </c>
       <c r="K18" t="n">
         <v>61</v>
@@ -1605,13 +1605,13 @@
         <v>56650000</v>
       </c>
       <c r="M18" t="n">
-        <v>8.33</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1634,16 +1634,16 @@
         <v>71500000</v>
       </c>
       <c r="G19" t="n">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="H19" t="n">
-        <v>482265000</v>
+        <v>481165000</v>
       </c>
       <c r="I19" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>2800000</v>
+        <v>1200000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1672,25 +1672,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F20" t="n">
-        <v>22250000</v>
+        <v>42000000</v>
       </c>
       <c r="G20" t="n">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="H20" t="n">
-        <v>380520000</v>
+        <v>396270000</v>
       </c>
       <c r="I20" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>32050000</v>
+        <v>21800000</v>
       </c>
       <c r="K20" t="n">
         <v>65</v>
@@ -1699,13 +1699,13 @@
         <v>63820000</v>
       </c>
       <c r="M20" t="n">
-        <v>16.77</v>
+        <v>16.11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,25 +1719,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F21" t="n">
-        <v>39100000</v>
+        <v>49600000</v>
       </c>
       <c r="G21" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="H21" t="n">
-        <v>491772000</v>
+        <v>494792000</v>
       </c>
       <c r="I21" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="J21" t="n">
-        <v>119950000</v>
+        <v>86210000</v>
       </c>
       <c r="K21" t="n">
         <v>86</v>
@@ -1746,13 +1746,13 @@
         <v>86822000</v>
       </c>
       <c r="M21" t="n">
-        <v>17.65</v>
+        <v>17.55</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,40 +1766,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F22" t="n">
-        <v>41700000</v>
+        <v>98400000</v>
       </c>
       <c r="G22" t="n">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="H22" t="n">
-        <v>710490000</v>
+        <v>758115000</v>
       </c>
       <c r="I22" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>52925000</v>
+        <v>21000000</v>
       </c>
       <c r="K22" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="L22" t="n">
-        <v>63025000</v>
+        <v>59575000</v>
       </c>
       <c r="M22" t="n">
-        <v>8.869999999999999</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1813,25 +1813,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F23" t="n">
-        <v>4200000</v>
+        <v>25200000</v>
       </c>
       <c r="G23" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="H23" t="n">
-        <v>90010000</v>
+        <v>110360000</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>4050000</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>44</v>
@@ -1840,13 +1840,13 @@
         <v>26710000</v>
       </c>
       <c r="M23" t="n">
-        <v>29.67</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,25 +1860,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>31500000</v>
       </c>
       <c r="G24" t="n">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="H24" t="n">
-        <v>354800000</v>
+        <v>385150000</v>
       </c>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J24" t="n">
-        <v>15450000</v>
+        <v>12750000</v>
       </c>
       <c r="K24" t="n">
         <v>13</v>
@@ -1887,7 +1887,7 @@
         <v>20850000</v>
       </c>
       <c r="M24" t="n">
-        <v>5.88</v>
+        <v>5.41</v>
       </c>
     </row>
   </sheetData>
@@ -2113,7 +2113,6 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>النجف</t>
@@ -2145,7 +2144,6 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>كربلاء</t>
@@ -2177,7 +2175,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>الحلة</t>
@@ -2209,7 +2206,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>الديوانية</t>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>547709000</v>
+        <v>517239000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>413808000</v>
+        <v>391599000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>370735001</v>
+        <v>361160001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>262477000</v>
+        <v>246372000</v>
       </c>
     </row>
   </sheetData>
@@ -517,61 +517,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>112100000</v>
+        <v>85500000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>103500000</v>
+        <v>57050000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>90400000</v>
+        <v>42000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>69600000</v>
+        <v>22800000</v>
       </c>
     </row>
   </sheetData>
@@ -2113,6 +2113,7 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>النجف</t>
@@ -2137,13 +2138,14 @@
         <v>324966000</v>
       </c>
       <c r="I2" t="n">
-        <v>242600000</v>
+        <v>409100000</v>
       </c>
       <c r="J2" t="n">
-        <v>413808000</v>
+        <v>391599000</v>
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>كربلاء</t>
@@ -2168,13 +2170,14 @@
         <v>194867000</v>
       </c>
       <c r="I3" t="n">
-        <v>178750000</v>
+        <v>318200000</v>
       </c>
       <c r="J3" t="n">
-        <v>262477000</v>
+        <v>246372000</v>
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>الحلة</t>
@@ -2199,13 +2202,14 @@
         <v>459416000</v>
       </c>
       <c r="I4" t="n">
-        <v>152900000</v>
+        <v>302160000</v>
       </c>
       <c r="J4" t="n">
-        <v>547709000</v>
+        <v>517239000</v>
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>الديوانية</t>
@@ -2230,10 +2234,10 @@
         <v>365124001</v>
       </c>
       <c r="I5" t="n">
-        <v>164520000</v>
+        <v>320720000</v>
       </c>
       <c r="J5" t="n">
-        <v>370735001</v>
+        <v>361160001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>88919000</v>
+        <v>217999000</v>
       </c>
     </row>
     <row r="3">
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>75623000</v>
+        <v>150316000</v>
       </c>
     </row>
     <row r="4">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>229435310</v>
+        <v>177528790</v>
       </c>
     </row>
     <row r="5">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>58814500</v>
+        <v>63046500</v>
       </c>
     </row>
     <row r="6">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>418449500</v>
+        <v>441469500</v>
       </c>
     </row>
     <row r="7">
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>134972330</v>
+        <v>71601120</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>517239000</v>
+        <v>514061000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>391599000</v>
+        <v>387174000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>361160001</v>
+        <v>360010001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>246372000</v>
+        <v>243922000</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -526,16 +526,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>85500000</v>
+        <v>84600000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>57050000</v>
+        <v>55800000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -565,13 +565,13 @@
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>42000000</v>
+        <v>52700000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>22800000</v>
+        <v>52200000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -650,7 +650,7 @@
         <v>2402</v>
       </c>
       <c r="E2" t="n">
-        <v>3436214000</v>
+        <v>3431639000</v>
       </c>
       <c r="F2" t="n">
         <v>404131000</v>
@@ -659,7 +659,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,22 +668,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>320720000</v>
+        <v>340520000</v>
       </c>
       <c r="D3" t="n">
-        <v>2275</v>
+        <v>2290</v>
       </c>
       <c r="E3" t="n">
-        <v>2868511000</v>
+        <v>2885621000</v>
       </c>
       <c r="F3" t="n">
-        <v>357680000</v>
+        <v>357480000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>318200000</v>
+        <v>332400000</v>
       </c>
       <c r="D4" t="n">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="E4" t="n">
-        <v>2625852000</v>
+        <v>2635702000</v>
       </c>
       <c r="F4" t="n">
         <v>257777000</v>
@@ -707,7 +707,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,13 +719,13 @@
         <v>302160000</v>
       </c>
       <c r="D5" t="n">
-        <v>2576</v>
+        <v>2573</v>
       </c>
       <c r="E5" t="n">
-        <v>3130438000</v>
+        <v>3125510000</v>
       </c>
       <c r="F5" t="n">
-        <v>500346000</v>
+        <v>498906000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -835,10 +835,10 @@
         <v>41900000</v>
       </c>
       <c r="G2" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="H2" t="n">
-        <v>562345000</v>
+        <v>561595000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -885,13 +885,13 @@
         <v>535</v>
       </c>
       <c r="H3" t="n">
-        <v>560916000</v>
+        <v>560056000</v>
       </c>
       <c r="I3" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J3" t="n">
-        <v>35845000</v>
+        <v>30605000</v>
       </c>
       <c r="K3" t="n">
         <v>194</v>
@@ -900,13 +900,13 @@
         <v>179331000</v>
       </c>
       <c r="M3" t="n">
-        <v>31.97</v>
+        <v>32.02</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -953,7 +953,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -979,13 +979,13 @@
         <v>458</v>
       </c>
       <c r="H5" t="n">
-        <v>833955000</v>
+        <v>832955000</v>
       </c>
       <c r="I5" t="n">
         <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>19325000</v>
+        <v>18325000</v>
       </c>
       <c r="K5" t="n">
         <v>21</v>
@@ -994,13 +994,13 @@
         <v>29395000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1026,28 +1026,28 @@
         <v>556</v>
       </c>
       <c r="H6" t="n">
-        <v>479762000</v>
+        <v>477444000</v>
       </c>
       <c r="I6" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="J6" t="n">
-        <v>67487000</v>
+        <v>59385000</v>
       </c>
       <c r="K6" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L6" t="n">
-        <v>115275000</v>
+        <v>113835000</v>
       </c>
       <c r="M6" t="n">
-        <v>24.03</v>
+        <v>23.84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1094,7 +1094,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1167,7 +1167,7 @@
         <v>231</v>
       </c>
       <c r="H9" t="n">
-        <v>287100000</v>
+        <v>286900000</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
@@ -1179,16 +1179,16 @@
         <v>92</v>
       </c>
       <c r="L9" t="n">
-        <v>71975000</v>
+        <v>71775000</v>
       </c>
       <c r="M9" t="n">
-        <v>25.07</v>
+        <v>25.02</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1214,13 +1214,13 @@
         <v>381</v>
       </c>
       <c r="H10" t="n">
-        <v>530190000</v>
+        <v>529690000</v>
       </c>
       <c r="I10" t="n">
         <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>9750000</v>
+        <v>9250000</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1261,13 +1261,13 @@
         <v>482</v>
       </c>
       <c r="H11" t="n">
-        <v>855454000</v>
+        <v>853464000</v>
       </c>
       <c r="I11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
-        <v>19350000</v>
+        <v>16650000</v>
       </c>
       <c r="K11" t="n">
         <v>17</v>
@@ -1276,13 +1276,13 @@
         <v>25575000</v>
       </c>
       <c r="M11" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F12" t="n">
-        <v>54300000</v>
+        <v>57900000</v>
       </c>
       <c r="G12" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="H12" t="n">
-        <v>436551000</v>
+        <v>440151000</v>
       </c>
       <c r="I12" t="n">
         <v>3</v>
@@ -1323,13 +1323,13 @@
         <v>55755000</v>
       </c>
       <c r="M12" t="n">
-        <v>12.77</v>
+        <v>12.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,19 +1343,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F13" t="n">
-        <v>25800000</v>
+        <v>42000000</v>
       </c>
       <c r="G13" t="n">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="H13" t="n">
-        <v>393155000</v>
+        <v>409355000</v>
       </c>
       <c r="I13" t="n">
         <v>58</v>
@@ -1370,13 +1370,13 @@
         <v>109245000</v>
       </c>
       <c r="M13" t="n">
-        <v>27.79</v>
+        <v>26.69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1423,7 +1423,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1449,13 +1449,13 @@
         <v>337</v>
       </c>
       <c r="H15" t="n">
-        <v>649220000</v>
+        <v>648570000</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>13500000</v>
+        <v>12000000</v>
       </c>
       <c r="K15" t="n">
         <v>51</v>
@@ -1464,13 +1464,13 @@
         <v>79275000</v>
       </c>
       <c r="M15" t="n">
-        <v>12.21</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1543,13 +1543,13 @@
         <v>600</v>
       </c>
       <c r="H17" t="n">
-        <v>975002000</v>
+        <v>971077000</v>
       </c>
       <c r="I17" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="J17" t="n">
-        <v>165721000</v>
+        <v>146096000</v>
       </c>
       <c r="K17" t="n">
         <v>75</v>
@@ -1558,13 +1558,13 @@
         <v>78950000</v>
       </c>
       <c r="M17" t="n">
-        <v>8.1</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>458</v>
       </c>
       <c r="H19" t="n">
-        <v>481165000</v>
+        <v>480265000</v>
       </c>
       <c r="I19" t="n">
         <v>3</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1672,25 +1672,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
+        <v>27</v>
+      </c>
+      <c r="F20" t="n">
+        <v>56200000</v>
+      </c>
+      <c r="G20" t="n">
+        <v>330</v>
+      </c>
+      <c r="H20" t="n">
+        <v>409670000</v>
+      </c>
+      <c r="I20" t="n">
         <v>18</v>
       </c>
-      <c r="F20" t="n">
-        <v>42000000</v>
-      </c>
-      <c r="G20" t="n">
-        <v>321</v>
-      </c>
-      <c r="H20" t="n">
-        <v>396270000</v>
-      </c>
-      <c r="I20" t="n">
-        <v>20</v>
-      </c>
       <c r="J20" t="n">
-        <v>21800000</v>
+        <v>16200000</v>
       </c>
       <c r="K20" t="n">
         <v>65</v>
@@ -1699,13 +1699,13 @@
         <v>63820000</v>
       </c>
       <c r="M20" t="n">
-        <v>16.11</v>
+        <v>15.58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1728,10 +1728,10 @@
         <v>49600000</v>
       </c>
       <c r="G21" t="n">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H21" t="n">
-        <v>494792000</v>
+        <v>493792000</v>
       </c>
       <c r="I21" t="n">
         <v>100</v>
@@ -1746,13 +1746,13 @@
         <v>86822000</v>
       </c>
       <c r="M21" t="n">
-        <v>17.55</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1775,16 +1775,16 @@
         <v>98400000</v>
       </c>
       <c r="G22" t="n">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="H22" t="n">
-        <v>758115000</v>
+        <v>756465000</v>
       </c>
       <c r="I22" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J22" t="n">
-        <v>21000000</v>
+        <v>15900000</v>
       </c>
       <c r="K22" t="n">
         <v>36</v>
@@ -1793,13 +1793,13 @@
         <v>59575000</v>
       </c>
       <c r="M22" t="n">
-        <v>7.86</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>150316000</v>
+        <v>147517000</v>
       </c>
     </row>
     <row r="4">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>177528790</v>
+        <v>164836790</v>
       </c>
     </row>
     <row r="5">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63046500</v>
+        <v>48635500</v>
       </c>
     </row>
     <row r="6">
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>71601120</v>
+        <v>62624760</v>
       </c>
     </row>
   </sheetData>
@@ -2141,7 +2141,7 @@
         <v>409100000</v>
       </c>
       <c r="J2" t="n">
-        <v>391599000</v>
+        <v>387174000</v>
       </c>
     </row>
     <row r="3">
@@ -2170,10 +2170,10 @@
         <v>194867000</v>
       </c>
       <c r="I3" t="n">
-        <v>318200000</v>
+        <v>332400000</v>
       </c>
       <c r="J3" t="n">
-        <v>246372000</v>
+        <v>243922000</v>
       </c>
     </row>
     <row r="4">
@@ -2205,7 +2205,7 @@
         <v>302160000</v>
       </c>
       <c r="J4" t="n">
-        <v>517239000</v>
+        <v>514061000</v>
       </c>
     </row>
     <row r="5">
@@ -2234,10 +2234,10 @@
         <v>365124001</v>
       </c>
       <c r="I5" t="n">
-        <v>320720000</v>
+        <v>340520000</v>
       </c>
       <c r="J5" t="n">
-        <v>361160001</v>
+        <v>360010001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>514061000</v>
+        <v>509516000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>387174000</v>
+        <v>382051000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>360010001</v>
+        <v>359600001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>243922000</v>
+        <v>239122000</v>
       </c>
     </row>
   </sheetData>
@@ -517,73 +517,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>84600000</v>
+        <v>81300000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>55800000</v>
+        <v>73200000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>كربلاء</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>52700000</v>
+        <v>70200000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>كربلاء</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>52200000</v>
+        <v>58900000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,22 +644,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>409100000</v>
+        <v>472700000</v>
       </c>
       <c r="D2" t="n">
-        <v>2402</v>
+        <v>2412</v>
       </c>
       <c r="E2" t="n">
-        <v>3431639000</v>
+        <v>3481741000</v>
       </c>
       <c r="F2" t="n">
-        <v>404131000</v>
+        <v>402881000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>340520000</v>
+        <v>364520000</v>
       </c>
       <c r="D3" t="n">
-        <v>2290</v>
+        <v>2303</v>
       </c>
       <c r="E3" t="n">
-        <v>2885621000</v>
+        <v>2907461000</v>
       </c>
       <c r="F3" t="n">
         <v>357480000</v>
@@ -683,7 +683,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>332400000</v>
+        <v>353600000</v>
       </c>
       <c r="D4" t="n">
-        <v>2176</v>
+        <v>2187</v>
       </c>
       <c r="E4" t="n">
-        <v>2635702000</v>
+        <v>2649227000</v>
       </c>
       <c r="F4" t="n">
         <v>257777000</v>
@@ -707,7 +707,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,13 +719,13 @@
         <v>302160000</v>
       </c>
       <c r="D5" t="n">
-        <v>2573</v>
+        <v>2567</v>
       </c>
       <c r="E5" t="n">
-        <v>3125510000</v>
+        <v>3117783000</v>
       </c>
       <c r="F5" t="n">
-        <v>498906000</v>
+        <v>498306000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -838,7 +838,7 @@
         <v>355</v>
       </c>
       <c r="H2" t="n">
-        <v>561595000</v>
+        <v>561220000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -885,13 +885,13 @@
         <v>535</v>
       </c>
       <c r="H3" t="n">
-        <v>560056000</v>
+        <v>558524000</v>
       </c>
       <c r="I3" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J3" t="n">
-        <v>30605000</v>
+        <v>25205000</v>
       </c>
       <c r="K3" t="n">
         <v>194</v>
@@ -900,13 +900,13 @@
         <v>179331000</v>
       </c>
       <c r="M3" t="n">
-        <v>32.02</v>
+        <v>32.11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,31 +929,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H4" t="n">
-        <v>158200000</v>
+        <v>155650000</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
-        <v>5460000</v>
+        <v>5010000</v>
       </c>
       <c r="K4" t="n">
         <v>106</v>
       </c>
       <c r="L4" t="n">
-        <v>126415000</v>
+        <v>125815000</v>
       </c>
       <c r="M4" t="n">
-        <v>79.91</v>
+        <v>80.83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -976,16 +976,16 @@
         <v>122960000</v>
       </c>
       <c r="G5" t="n">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="H5" t="n">
-        <v>832955000</v>
+        <v>832005000</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J5" t="n">
-        <v>18325000</v>
+        <v>17375000</v>
       </c>
       <c r="K5" t="n">
         <v>21</v>
@@ -1000,7 +1000,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1026,13 +1026,13 @@
         <v>556</v>
       </c>
       <c r="H6" t="n">
-        <v>477444000</v>
+        <v>476859000</v>
       </c>
       <c r="I6" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="J6" t="n">
-        <v>59385000</v>
+        <v>55380000</v>
       </c>
       <c r="K6" t="n">
         <v>148</v>
@@ -1041,13 +1041,13 @@
         <v>113835000</v>
       </c>
       <c r="M6" t="n">
-        <v>23.84</v>
+        <v>23.87</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1073,13 +1073,13 @@
         <v>501</v>
       </c>
       <c r="H7" t="n">
-        <v>535260000</v>
+        <v>533525000</v>
       </c>
       <c r="I7" t="n">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="J7" t="n">
-        <v>92675000</v>
+        <v>85260000</v>
       </c>
       <c r="K7" t="n">
         <v>45</v>
@@ -1088,13 +1088,13 @@
         <v>49930000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.33</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,19 +1108,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F8" t="n">
-        <v>41700000</v>
+        <v>47700000</v>
       </c>
       <c r="G8" t="n">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="H8" t="n">
-        <v>366061000</v>
+        <v>372061000</v>
       </c>
       <c r="I8" t="n">
         <v>42</v>
@@ -1135,13 +1135,13 @@
         <v>86630000</v>
       </c>
       <c r="M8" t="n">
-        <v>23.67</v>
+        <v>23.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F9" t="n">
-        <v>37620000</v>
+        <v>48420000</v>
       </c>
       <c r="G9" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="H9" t="n">
-        <v>286900000</v>
+        <v>297700000</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
@@ -1182,13 +1182,13 @@
         <v>71775000</v>
       </c>
       <c r="M9" t="n">
-        <v>25.02</v>
+        <v>24.11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1211,16 +1211,16 @@
         <v>70400000</v>
       </c>
       <c r="G10" t="n">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="H10" t="n">
-        <v>529690000</v>
+        <v>528290000</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>9250000</v>
+        <v>7000000</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
@@ -1229,13 +1229,13 @@
         <v>8500000</v>
       </c>
       <c r="M10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F12" t="n">
-        <v>57900000</v>
+        <v>61500000</v>
       </c>
       <c r="G12" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H12" t="n">
-        <v>440151000</v>
+        <v>443751000</v>
       </c>
       <c r="I12" t="n">
         <v>3</v>
@@ -1323,13 +1323,13 @@
         <v>55755000</v>
       </c>
       <c r="M12" t="n">
-        <v>12.67</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,25 +1343,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F13" t="n">
-        <v>42000000</v>
+        <v>45600000</v>
       </c>
       <c r="G13" t="n">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="H13" t="n">
-        <v>409355000</v>
+        <v>412195000</v>
       </c>
       <c r="I13" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J13" t="n">
-        <v>35220000</v>
+        <v>32340000</v>
       </c>
       <c r="K13" t="n">
         <v>138</v>
@@ -1370,13 +1370,13 @@
         <v>109245000</v>
       </c>
       <c r="M13" t="n">
-        <v>26.69</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1423,7 +1423,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1437,19 +1437,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F15" t="n">
-        <v>95400000</v>
+        <v>107400000</v>
       </c>
       <c r="G15" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H15" t="n">
-        <v>648570000</v>
+        <v>659920000</v>
       </c>
       <c r="I15" t="n">
         <v>4</v>
@@ -1464,13 +1464,13 @@
         <v>79275000</v>
       </c>
       <c r="M15" t="n">
-        <v>12.22</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1484,25 +1484,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F16" t="n">
-        <v>79800000</v>
+        <v>85800000</v>
       </c>
       <c r="G16" t="n">
         <v>329</v>
       </c>
       <c r="H16" t="n">
-        <v>410345000</v>
+        <v>414670000</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>1785000</v>
+        <v>360000</v>
       </c>
       <c r="K16" t="n">
         <v>98</v>
@@ -1511,13 +1511,13 @@
         <v>121775000</v>
       </c>
       <c r="M16" t="n">
-        <v>29.68</v>
+        <v>29.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,25 +1531,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F17" t="n">
-        <v>79000000</v>
+        <v>89800000</v>
       </c>
       <c r="G17" t="n">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="H17" t="n">
-        <v>971077000</v>
+        <v>977454000</v>
       </c>
       <c r="I17" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="J17" t="n">
-        <v>146096000</v>
+        <v>134800000</v>
       </c>
       <c r="K17" t="n">
         <v>75</v>
@@ -1558,13 +1558,13 @@
         <v>78950000</v>
       </c>
       <c r="M17" t="n">
-        <v>8.130000000000001</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,40 +1578,40 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E18" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="F18" t="n">
-        <v>65800000</v>
+        <v>100600000</v>
       </c>
       <c r="G18" t="n">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="H18" t="n">
-        <v>683687000</v>
+        <v>711737000</v>
       </c>
       <c r="I18" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>23500000</v>
+        <v>5750000</v>
       </c>
       <c r="K18" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="L18" t="n">
-        <v>56650000</v>
+        <v>55400000</v>
       </c>
       <c r="M18" t="n">
-        <v>8.289999999999999</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1634,16 +1634,16 @@
         <v>71500000</v>
       </c>
       <c r="G19" t="n">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H19" t="n">
-        <v>480265000</v>
+        <v>479365000</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1672,25 +1672,25 @@
         </is>
       </c>
       <c r="D20" t="n">
+        <v>14</v>
+      </c>
+      <c r="E20" t="n">
+        <v>32</v>
+      </c>
+      <c r="F20" t="n">
+        <v>59700000</v>
+      </c>
+      <c r="G20" t="n">
+        <v>335</v>
+      </c>
+      <c r="H20" t="n">
+        <v>410320000</v>
+      </c>
+      <c r="I20" t="n">
         <v>12</v>
       </c>
-      <c r="E20" t="n">
-        <v>27</v>
-      </c>
-      <c r="F20" t="n">
-        <v>56200000</v>
-      </c>
-      <c r="G20" t="n">
-        <v>330</v>
-      </c>
-      <c r="H20" t="n">
-        <v>409670000</v>
-      </c>
-      <c r="I20" t="n">
-        <v>18</v>
-      </c>
       <c r="J20" t="n">
-        <v>16200000</v>
+        <v>4950000</v>
       </c>
       <c r="K20" t="n">
         <v>65</v>
@@ -1699,13 +1699,13 @@
         <v>63820000</v>
       </c>
       <c r="M20" t="n">
-        <v>15.58</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,25 +1719,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F21" t="n">
-        <v>49600000</v>
+        <v>63800000</v>
       </c>
       <c r="G21" t="n">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="H21" t="n">
-        <v>493792000</v>
+        <v>506492000</v>
       </c>
       <c r="I21" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="J21" t="n">
-        <v>86210000</v>
+        <v>80960000</v>
       </c>
       <c r="K21" t="n">
         <v>86</v>
@@ -1746,13 +1746,13 @@
         <v>86822000</v>
       </c>
       <c r="M21" t="n">
-        <v>17.58</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1775,16 +1775,16 @@
         <v>98400000</v>
       </c>
       <c r="G22" t="n">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="H22" t="n">
-        <v>756465000</v>
+        <v>754490000</v>
       </c>
       <c r="I22" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J22" t="n">
-        <v>15900000</v>
+        <v>14250000</v>
       </c>
       <c r="K22" t="n">
         <v>36</v>
@@ -1793,13 +1793,13 @@
         <v>59575000</v>
       </c>
       <c r="M22" t="n">
-        <v>7.88</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,25 +1860,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F24" t="n">
-        <v>31500000</v>
+        <v>35000000</v>
       </c>
       <c r="G24" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="H24" t="n">
-        <v>385150000</v>
+        <v>388200000</v>
       </c>
       <c r="I24" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J24" t="n">
-        <v>12750000</v>
+        <v>10950000</v>
       </c>
       <c r="K24" t="n">
         <v>13</v>
@@ -1887,7 +1887,7 @@
         <v>20850000</v>
       </c>
       <c r="M24" t="n">
-        <v>5.41</v>
+        <v>5.37</v>
       </c>
     </row>
   </sheetData>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>147517000</v>
+        <v>121334000</v>
       </c>
     </row>
     <row r="4">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>164836790</v>
+        <v>140907790</v>
       </c>
     </row>
     <row r="5">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>48635500</v>
+        <v>84828500</v>
       </c>
     </row>
     <row r="6">
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>62624760</v>
+        <v>61744760</v>
       </c>
     </row>
   </sheetData>
@@ -2138,10 +2138,10 @@
         <v>324966000</v>
       </c>
       <c r="I2" t="n">
-        <v>409100000</v>
+        <v>472700000</v>
       </c>
       <c r="J2" t="n">
-        <v>387174000</v>
+        <v>382051000</v>
       </c>
     </row>
     <row r="3">
@@ -2170,10 +2170,10 @@
         <v>194867000</v>
       </c>
       <c r="I3" t="n">
-        <v>332400000</v>
+        <v>353600000</v>
       </c>
       <c r="J3" t="n">
-        <v>243922000</v>
+        <v>239122000</v>
       </c>
     </row>
     <row r="4">
@@ -2205,7 +2205,7 @@
         <v>302160000</v>
       </c>
       <c r="J4" t="n">
-        <v>514061000</v>
+        <v>509516000</v>
       </c>
     </row>
     <row r="5">
@@ -2234,10 +2234,10 @@
         <v>365124001</v>
       </c>
       <c r="I5" t="n">
-        <v>340520000</v>
+        <v>364520000</v>
       </c>
       <c r="J5" t="n">
-        <v>360010001</v>
+        <v>359600001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>509516000</v>
+        <v>506681000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>382051000</v>
+        <v>371966000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>359600001</v>
+        <v>356265001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>239122000</v>
+        <v>238122000</v>
       </c>
     </row>
   </sheetData>
@@ -517,61 +517,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>81300000</v>
+        <v>81600000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>73200000</v>
+        <v>72400000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>70200000</v>
+        <v>63900000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>58900000</v>
+        <v>44500000</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>472700000</v>
+        <v>506300000</v>
       </c>
       <c r="D2" t="n">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="E2" t="n">
-        <v>3481741000</v>
+        <v>3501841000</v>
       </c>
       <c r="F2" t="n">
         <v>402881000</v>
@@ -659,7 +659,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>364520000</v>
+        <v>387620000</v>
       </c>
       <c r="D3" t="n">
-        <v>2303</v>
+        <v>2314</v>
       </c>
       <c r="E3" t="n">
-        <v>2907461000</v>
+        <v>2926866000</v>
       </c>
       <c r="F3" t="n">
         <v>357480000</v>
@@ -683,7 +683,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>353600000</v>
+        <v>384500000</v>
       </c>
       <c r="D4" t="n">
-        <v>2187</v>
+        <v>2202</v>
       </c>
       <c r="E4" t="n">
-        <v>2649227000</v>
+        <v>2673152000</v>
       </c>
       <c r="F4" t="n">
-        <v>257777000</v>
+        <v>250777000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>302160000</v>
+        <v>345360000</v>
       </c>
       <c r="D5" t="n">
-        <v>2567</v>
+        <v>2585</v>
       </c>
       <c r="E5" t="n">
-        <v>3117783000</v>
+        <v>3153973000</v>
       </c>
       <c r="F5" t="n">
-        <v>498306000</v>
+        <v>494526000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F2" t="n">
-        <v>41900000</v>
+        <v>62000000</v>
       </c>
       <c r="G2" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="H2" t="n">
-        <v>561220000</v>
+        <v>577820000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,25 +873,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
-        <v>37200000</v>
+        <v>40200000</v>
       </c>
       <c r="G3" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="H3" t="n">
-        <v>558524000</v>
+        <v>560324000</v>
       </c>
       <c r="I3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J3" t="n">
-        <v>25205000</v>
+        <v>22505000</v>
       </c>
       <c r="K3" t="n">
         <v>194</v>
@@ -900,13 +900,13 @@
         <v>179331000</v>
       </c>
       <c r="M3" t="n">
-        <v>32.11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -953,7 +953,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1000,7 +1000,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1026,13 +1026,13 @@
         <v>556</v>
       </c>
       <c r="H6" t="n">
-        <v>476859000</v>
+        <v>476259000</v>
       </c>
       <c r="I6" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="J6" t="n">
-        <v>55380000</v>
+        <v>50370000</v>
       </c>
       <c r="K6" t="n">
         <v>148</v>
@@ -1041,13 +1041,13 @@
         <v>113835000</v>
       </c>
       <c r="M6" t="n">
-        <v>23.87</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1061,40 +1061,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F7" t="n">
-        <v>47100000</v>
+        <v>67200000</v>
       </c>
       <c r="G7" t="n">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="H7" t="n">
-        <v>533525000</v>
+        <v>551915000</v>
       </c>
       <c r="I7" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="J7" t="n">
-        <v>85260000</v>
+        <v>79050000</v>
       </c>
       <c r="K7" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="L7" t="n">
-        <v>49930000</v>
+        <v>46150000</v>
       </c>
       <c r="M7" t="n">
-        <v>9.359999999999999</v>
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1108,25 +1108,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F8" t="n">
-        <v>47700000</v>
+        <v>51900000</v>
       </c>
       <c r="G8" t="n">
         <v>362</v>
       </c>
       <c r="H8" t="n">
-        <v>372061000</v>
+        <v>374386000</v>
       </c>
       <c r="I8" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="J8" t="n">
-        <v>22240000</v>
+        <v>15190000</v>
       </c>
       <c r="K8" t="n">
         <v>116</v>
@@ -1135,13 +1135,13 @@
         <v>86630000</v>
       </c>
       <c r="M8" t="n">
-        <v>23.28</v>
+        <v>23.14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F9" t="n">
-        <v>48420000</v>
+        <v>61320000</v>
       </c>
       <c r="G9" t="n">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="H9" t="n">
-        <v>297700000</v>
+        <v>310240000</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
@@ -1182,13 +1182,13 @@
         <v>71775000</v>
       </c>
       <c r="M9" t="n">
-        <v>24.11</v>
+        <v>23.14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1329,7 +1329,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1343,25 +1343,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F13" t="n">
-        <v>45600000</v>
+        <v>51600000</v>
       </c>
       <c r="G13" t="n">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="H13" t="n">
-        <v>412195000</v>
+        <v>416735000</v>
       </c>
       <c r="I13" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J13" t="n">
-        <v>32340000</v>
+        <v>23820000</v>
       </c>
       <c r="K13" t="n">
         <v>138</v>
@@ -1370,13 +1370,13 @@
         <v>109245000</v>
       </c>
       <c r="M13" t="n">
-        <v>26.5</v>
+        <v>26.21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1402,13 +1402,13 @@
         <v>558</v>
       </c>
       <c r="H14" t="n">
-        <v>717960000</v>
+        <v>714110000</v>
       </c>
       <c r="I14" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>31420000</v>
+        <v>17120000</v>
       </c>
       <c r="K14" t="n">
         <v>87</v>
@@ -1417,13 +1417,13 @@
         <v>67481000</v>
       </c>
       <c r="M14" t="n">
-        <v>9.4</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1470,7 +1470,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1493,16 +1493,16 @@
         <v>85800000</v>
       </c>
       <c r="G16" t="n">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H16" t="n">
-        <v>414670000</v>
+        <v>414310000</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>360000</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>98</v>
@@ -1511,13 +1511,13 @@
         <v>121775000</v>
       </c>
       <c r="M16" t="n">
-        <v>29.37</v>
+        <v>29.39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1531,25 +1531,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F17" t="n">
-        <v>89800000</v>
+        <v>123400000</v>
       </c>
       <c r="G17" t="n">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="H17" t="n">
-        <v>977454000</v>
+        <v>1001764000</v>
       </c>
       <c r="I17" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="J17" t="n">
-        <v>134800000</v>
+        <v>112850000</v>
       </c>
       <c r="K17" t="n">
         <v>75</v>
@@ -1558,13 +1558,13 @@
         <v>78950000</v>
       </c>
       <c r="M17" t="n">
-        <v>8.08</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1684,7 +1684,7 @@
         <v>335</v>
       </c>
       <c r="H20" t="n">
-        <v>410320000</v>
+        <v>409870000</v>
       </c>
       <c r="I20" t="n">
         <v>12</v>
@@ -1699,13 +1699,13 @@
         <v>63820000</v>
       </c>
       <c r="M20" t="n">
-        <v>15.55</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1719,19 +1719,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F21" t="n">
-        <v>63800000</v>
+        <v>74300000</v>
       </c>
       <c r="G21" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="H21" t="n">
-        <v>506492000</v>
+        <v>515642000</v>
       </c>
       <c r="I21" t="n">
         <v>91</v>
@@ -1746,13 +1746,13 @@
         <v>86822000</v>
       </c>
       <c r="M21" t="n">
-        <v>17.14</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1778,28 +1778,28 @@
         <v>498</v>
       </c>
       <c r="H22" t="n">
-        <v>754490000</v>
+        <v>753490000</v>
       </c>
       <c r="I22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J22" t="n">
-        <v>14250000</v>
+        <v>20250000</v>
       </c>
       <c r="K22" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L22" t="n">
-        <v>59575000</v>
+        <v>52575000</v>
       </c>
       <c r="M22" t="n">
-        <v>7.9</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1860,19 +1860,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E24" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F24" t="n">
-        <v>35000000</v>
+        <v>55400000</v>
       </c>
       <c r="G24" t="n">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="H24" t="n">
-        <v>388200000</v>
+        <v>404425000</v>
       </c>
       <c r="I24" t="n">
         <v>11</v>
@@ -1887,7 +1887,7 @@
         <v>20850000</v>
       </c>
       <c r="M24" t="n">
-        <v>5.37</v>
+        <v>5.16</v>
       </c>
     </row>
   </sheetData>
@@ -1929,7 +1929,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1949,7 +1949,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1963,13 +1963,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>121334000</v>
+        <v>112164000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>140907790</v>
+        <v>121634790</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2009,7 +2009,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2029,7 +2029,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>61744760</v>
+        <v>57367500</v>
       </c>
     </row>
   </sheetData>
@@ -2138,10 +2138,10 @@
         <v>324966000</v>
       </c>
       <c r="I2" t="n">
-        <v>472700000</v>
+        <v>506300000</v>
       </c>
       <c r="J2" t="n">
-        <v>382051000</v>
+        <v>371966000</v>
       </c>
     </row>
     <row r="3">
@@ -2170,10 +2170,10 @@
         <v>194867000</v>
       </c>
       <c r="I3" t="n">
-        <v>353600000</v>
+        <v>384500000</v>
       </c>
       <c r="J3" t="n">
-        <v>239122000</v>
+        <v>238122000</v>
       </c>
     </row>
     <row r="4">
@@ -2202,10 +2202,10 @@
         <v>459416000</v>
       </c>
       <c r="I4" t="n">
-        <v>302160000</v>
+        <v>345360000</v>
       </c>
       <c r="J4" t="n">
-        <v>509516000</v>
+        <v>506681000</v>
       </c>
     </row>
     <row r="5">
@@ -2234,10 +2234,10 @@
         <v>365124001</v>
       </c>
       <c r="I5" t="n">
-        <v>364520000</v>
+        <v>387620000</v>
       </c>
       <c r="J5" t="n">
-        <v>359600001</v>
+        <v>356265001</v>
       </c>
     </row>
   </sheetData>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -2113,7 +2113,6 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>النجف</t>
@@ -2145,7 +2144,6 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>كربلاء</t>
@@ -2177,7 +2175,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>الحلة</t>
@@ -2209,7 +2206,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>الديوانية</t>

--- a/output/dashboard_output.xlsx
+++ b/output/dashboard_output.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>506681000</v>
+        <v>495406000</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>371966000</v>
+        <v>362056000</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>356265001</v>
+        <v>347945001</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>238122000</v>
+        <v>233257000</v>
       </c>
     </row>
   </sheetData>
@@ -517,61 +517,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>النجف</t>
+          <t>الديوانية</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>81600000</v>
+        <v>72900000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>الحلة</t>
+          <t>النجف</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>72400000</v>
+        <v>63900000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>الديوانية</t>
+          <t>الحلة</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>63900000</v>
+        <v>49650000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -644,22 +644,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>506300000</v>
+        <v>524000000</v>
       </c>
       <c r="D2" t="n">
-        <v>2411</v>
+        <v>2408</v>
       </c>
       <c r="E2" t="n">
-        <v>3501841000</v>
+        <v>3490231000</v>
       </c>
       <c r="F2" t="n">
-        <v>402881000</v>
+        <v>400181000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -671,19 +671,19 @@
         <v>387620000</v>
       </c>
       <c r="D3" t="n">
-        <v>2314</v>
+        <v>2305</v>
       </c>
       <c r="E3" t="n">
-        <v>2926866000</v>
+        <v>2912647000</v>
       </c>
       <c r="F3" t="n">
-        <v>357480000</v>
+        <v>356080000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -695,19 +695,19 @@
         <v>384500000</v>
       </c>
       <c r="D4" t="n">
-        <v>2202</v>
+        <v>2191</v>
       </c>
       <c r="E4" t="n">
-        <v>2673152000</v>
+        <v>2663987000</v>
       </c>
       <c r="F4" t="n">
-        <v>250777000</v>
+        <v>246967000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>345360000</v>
+        <v>379860000</v>
       </c>
       <c r="D5" t="n">
-        <v>2585</v>
+        <v>2597</v>
       </c>
       <c r="E5" t="n">
-        <v>3153973000</v>
+        <v>3170303000</v>
       </c>
       <c r="F5" t="n">
-        <v>494526000</v>
+        <v>492826000</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>62000000</v>
+        <v>84500000</v>
       </c>
       <c r="G2" t="n">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="H2" t="n">
-        <v>577820000</v>
+        <v>596995000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -873,40 +873,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F3" t="n">
-        <v>40200000</v>
+        <v>52200000</v>
       </c>
       <c r="G3" t="n">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="H3" t="n">
-        <v>560324000</v>
+        <v>570239000</v>
       </c>
       <c r="I3" t="n">
         <v>27</v>
       </c>
       <c r="J3" t="n">
-        <v>22505000</v>
+        <v>21980000</v>
       </c>
       <c r="K3" t="n">
         <v>194</v>
       </c>
       <c r="L3" t="n">
-        <v>179331000</v>
+        <v>179031000</v>
       </c>
       <c r="M3" t="n">
-        <v>32</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -953,7 +953,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -976,31 +976,31 @@
         <v>122960000</v>
       </c>
       <c r="G5" t="n">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="H5" t="n">
-        <v>832005000</v>
+        <v>830230000</v>
       </c>
       <c r="I5" t="n">
         <v>9</v>
       </c>
       <c r="J5" t="n">
-        <v>17375000</v>
+        <v>17600000</v>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>29395000</v>
+        <v>27995000</v>
       </c>
       <c r="M5" t="n">
-        <v>3.53</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1026,13 +1026,13 @@
         <v>556</v>
       </c>
       <c r="H6" t="n">
-        <v>476259000</v>
+        <v>474029000</v>
       </c>
       <c r="I6" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="J6" t="n">
-        <v>50370000</v>
+        <v>39560000</v>
       </c>
       <c r="K6" t="n">
         <v>148</v>
@@ -1041,13 +1041,13 @@
         <v>113835000</v>
       </c>
       <c r="M6" t="n">
-        <v>23.9</v>
+        <v>24.01</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1070,16 +1070,16 @@
         <v>67200000</v>
       </c>
       <c r="G7" t="n">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="H7" t="n">
-        <v>551915000</v>
+        <v>543160000</v>
       </c>
       <c r="I7" t="n">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="J7" t="n">
-        <v>79050000</v>
+        <v>42580000</v>
       </c>
       <c r="K7" t="n">
         <v>42</v>
@@ -1088,13 +1088,13 @@
         <v>46150000</v>
       </c>
       <c r="M7" t="n">
-        <v>8.359999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1117,16 +1117,16 @@
         <v>51900000</v>
       </c>
       <c r="G8" t="n">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="H8" t="n">
-        <v>374386000</v>
+        <v>371146000</v>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J8" t="n">
-        <v>15190000</v>
+        <v>5950000</v>
       </c>
       <c r="K8" t="n">
         <v>116</v>
@@ -1135,13 +1135,13 @@
         <v>86630000</v>
       </c>
       <c r="M8" t="n">
-        <v>23.14</v>
+        <v>23.34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1167,13 +1167,13 @@
         <v>245</v>
       </c>
       <c r="H9" t="n">
-        <v>310240000</v>
+        <v>309480000</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>7240000</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>92</v>
@@ -1182,13 +1182,13 @@
         <v>71775000</v>
       </c>
       <c r="M9" t="n">
-        <v>23.14</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1258,16 +1258,16 @@
         <v>90900000</v>
       </c>
       <c r="G11" t="n">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H11" t="n">
-        <v>853464000</v>
+        <v>847985000</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>16650000</v>
+        <v>12000000</v>
       </c>
       <c r="K11" t="n">
         <v>17</v>
@@ -1276,13 +1276,13 @@
         <v>25575000</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1308,28 +1308,28 @@
         <v>395</v>
       </c>
       <c r="H12" t="n">
-        <v>443751000</v>
+        <v>441591000</v>
       </c>
       <c r="I12" t="n">
         <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>6500000</v>
+        <v>6000000</v>
       </c>
       <c r="K12" t="n">
         <v>56</v>
       </c>
       <c r="L12" t="n">
-        <v>55755000</v>
+        <v>55555000</v>
       </c>
       <c r="M12" t="n">
-        <v>12.56</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1355,28 +1355,28 @@
         <v>452</v>
       </c>
       <c r="H13" t="n">
-        <v>416735000</v>
+        <v>414155000</v>
       </c>
       <c r="I13" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J13" t="n">
-        <v>23820000</v>
+        <v>12960000</v>
       </c>
       <c r="K13" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="L13" t="n">
-        <v>109245000</v>
+        <v>108045000</v>
       </c>
       <c r="M13" t="n">
-        <v>26.21</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1399,16 +1399,16 @@
         <v>89100000</v>
       </c>
       <c r="G14" t="n">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="H14" t="n">
-        <v>714110000</v>
+        <v>707750000</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>17120000</v>
+        <v>16160000</v>
       </c>
       <c r="K14" t="n">
         <v>87</v>
@@ -1417,13 +1417,13 @@
         <v>67481000</v>
       </c>
       <c r="M14" t="n">
-        <v>9.449999999999999</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1449,13 +1449,13 @@
         <v>339</v>
       </c>
       <c r="H15" t="n">
-        <v>659920000</v>
+        <v>656620000</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>12000000</v>
+        <v>6000000</v>
       </c>
       <c r="K15" t="n">
         <v>51</v>
@@ -1464,13 +1464,13 @@
         <v>79275000</v>
       </c>
       <c r="M15" t="n">
-        <v>12.01</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1496,7 +1496,7 @@
         <v>326</v>
       </c>
       <c r="H16" t="n">
-        <v>414310000</v>
+        <v>413610000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1511,13 +1511,13 @@
         <v>121775000</v>
       </c>
       <c r="M16" t="n">
-        <v>29.39</v>
+        <v>29.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1540,31 +1540,31 @@
         <v>123400000</v>
       </c>
       <c r="G17" t="n">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="H17" t="n">
-        <v>1001764000</v>
+        <v>990114000</v>
       </c>
       <c r="I17" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="J17" t="n">
-        <v>112850000</v>
+        <v>74075000</v>
       </c>
       <c r="K17" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L17" t="n">
-        <v>78950000</v>
+        <v>76250000</v>
       </c>
       <c r="M17" t="n">
-        <v>7.88</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1578,25 +1578,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E18" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F18" t="n">
-        <v>100600000</v>
+        <v>118300000</v>
       </c>
       <c r="G18" t="n">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="H18" t="n">
-        <v>711737000</v>
+        <v>722137000</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>5750000</v>
+        <v>250000</v>
       </c>
       <c r="K18" t="n">
         <v>58</v>
@@ -1605,13 +1605,13 @@
         <v>55400000</v>
       </c>
       <c r="M18" t="n">
-        <v>7.78</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>456</v>
       </c>
       <c r="H19" t="n">
-        <v>479365000</v>
+        <v>478965000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1681,16 +1681,16 @@
         <v>59700000</v>
       </c>
       <c r="G20" t="n">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H20" t="n">
-        <v>409870000</v>
+        <v>408020000</v>
       </c>
       <c r="I20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>4950000</v>
+        <v>3450000</v>
       </c>
       <c r="K20" t="n">
         <v>65</v>
@@ -1699,13 +1699,13 @@
         <v>63820000</v>
       </c>
       <c r="M20" t="n">
-        <v>15.57</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1728,31 +1728,31 @@
         <v>74300000</v>
       </c>
       <c r="G21" t="n">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="H21" t="n">
-        <v>515642000</v>
+        <v>511627000</v>
       </c>
       <c r="I21" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="J21" t="n">
-        <v>80960000</v>
+        <v>68740000</v>
       </c>
       <c r="K21" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="L21" t="n">
-        <v>86822000</v>
+        <v>83012000</v>
       </c>
       <c r="M21" t="n">
-        <v>16.84</v>
+        <v>16.23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1775,10 +1775,10 @@
         <v>98400000</v>
       </c>
       <c r="G22" t="n">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="H22" t="n">
-        <v>753490000</v>
+        <v>751540000</v>
       </c>
       <c r="I22" t="n">
         <v>11</v>
@@ -1793,13 +1793,13 @@
         <v>52575000</v>
       </c>
       <c r="M22" t="n">
-        <v>6.98</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1872,13 +1872,13 @@
         <v>312</v>
       </c>
       <c r="H24" t="n">
-        <v>404425000</v>
+        <v>403475000</v>
       </c>
       <c r="I24" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J24" t="n">
-        <v>10950000</v>
+        <v>7750000</v>
       </c>
       <c r="K24" t="n">
         <v>13</v>
@@ -1887,7 +1887,7 @@
         <v>20850000</v>
       </c>
       <c r="M24" t="n">
-        <v>5.16</v>
+        <v>5.17</v>
       </c>
     </row>
   </sheetData>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>112164000</v>
+        <v>45729760</v>
       </c>
     </row>
     <row r="4">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>121634790</v>
+        <v>110378790</v>
       </c>
     </row>
     <row r="5">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>84828500</v>
+        <v>9621500</v>
       </c>
     </row>
     <row r="6">
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>57367500</v>
+        <v>45729760</v>
       </c>
     </row>
   </sheetData>
@@ -2113,6 +2113,7 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>النجف</t>
@@ -2137,13 +2138,14 @@
         <v>324966000</v>
       </c>
       <c r="I2" t="n">
-        <v>506300000</v>
+        <v>524000000</v>
       </c>
       <c r="J2" t="n">
-        <v>371966000</v>
+        <v>362056000</v>
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>كربلاء</t>
@@ -2171,10 +2173,11 @@
         <v>384500000</v>
       </c>
       <c r="J3" t="n">
-        <v>238122000</v>
+        <v>233257000</v>
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>الحلة</t>
@@ -2199,13 +2202,14 @@
         <v>459416000</v>
       </c>
       <c r="I4" t="n">
-        <v>345360000</v>
+        <v>379860000</v>
       </c>
       <c r="J4" t="n">
-        <v>506681000</v>
+        <v>495406000</v>
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>الديوانية</t>
@@ -2233,7 +2237,7 @@
         <v>387620000</v>
       </c>
       <c r="J5" t="n">
-        <v>356265001</v>
+        <v>347945001</v>
       </c>
     </row>
   </sheetData>
